--- a/CAP776 (PYTHON).xlsx
+++ b/CAP776 (PYTHON).xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\palak\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\palak\Downloads\776(clone)\776\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B2536E73-460D-4FC2-8B44-B8A788EA2FED}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{51051FB3-5E3F-4E8D-AB35-96B05F7E0056}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{327CE7B2-1886-45B8-951C-28CB36CE6AAF}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="62" uniqueCount="34">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="75" uniqueCount="40">
   <si>
     <t>My Data, My Code — Daily Log</t>
   </si>
@@ -137,6 +137,24 @@
   <si>
     <t>Relaxed</t>
   </si>
+  <si>
+    <t>Busy</t>
+  </si>
+  <si>
+    <t>Heavy travel &amp; long class day</t>
+  </si>
+  <si>
+    <t>Managed classes, self-study</t>
+  </si>
+  <si>
+    <t>Moderate class schedule with coding focus</t>
+  </si>
+  <si>
+    <t>Exhausted</t>
+  </si>
+  <si>
+    <t>Full lecture day with heavy travel schedule</t>
+  </si>
 </sst>
 </file>
 
@@ -145,7 +163,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="yyyy\-mm\-dd"/>
   </numFmts>
-  <fonts count="8" x14ac:knownFonts="1">
+  <fonts count="9" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -202,6 +220,12 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
   </fonts>
   <fills count="4">
     <fill>
@@ -223,7 +247,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -246,12 +270,27 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="medium">
+        <color rgb="FFC4C7C5"/>
+      </left>
+      <right style="medium">
+        <color rgb="FFC4C7C5"/>
+      </right>
+      <top style="medium">
+        <color rgb="FFC4C7C5"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="FFC4C7C5"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="17">
+  <cellXfs count="22">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1" applyFont="1"/>
@@ -288,9 +327,22 @@
     <xf numFmtId="14" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="5"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="1" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="14" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -606,7 +658,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6E7F1806-3D91-4029-8849-359DB02F0997}">
-  <dimension ref="A1:N377"/>
+  <dimension ref="A1:O376"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="15.21875" customWidth="1"/>
@@ -626,39 +678,39 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:14" ht="16.8" x14ac:dyDescent="0.3">
-      <c r="A1" s="15" t="s">
+      <c r="A1" s="17" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="15"/>
-      <c r="C1" s="15"/>
-      <c r="D1" s="15"/>
-      <c r="E1" s="15"/>
-      <c r="F1" s="15"/>
-      <c r="G1" s="15"/>
-      <c r="H1" s="15"/>
-      <c r="I1" s="15"/>
-      <c r="J1" s="15"/>
-      <c r="K1" s="15"/>
-      <c r="L1" s="15"/>
-      <c r="M1" s="15"/>
-      <c r="N1" s="15"/>
+      <c r="B1" s="17"/>
+      <c r="C1" s="17"/>
+      <c r="D1" s="17"/>
+      <c r="E1" s="17"/>
+      <c r="F1" s="17"/>
+      <c r="G1" s="17"/>
+      <c r="H1" s="17"/>
+      <c r="I1" s="17"/>
+      <c r="J1" s="17"/>
+      <c r="K1" s="17"/>
+      <c r="L1" s="17"/>
+      <c r="M1" s="17"/>
+      <c r="N1" s="17"/>
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A2" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="16" t="s">
+      <c r="B2" s="18" t="s">
         <v>23</v>
       </c>
-      <c r="C2" s="16"/>
-      <c r="D2" s="16"/>
+      <c r="C2" s="18"/>
+      <c r="D2" s="18"/>
       <c r="E2" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="F2" s="16">
+      <c r="F2" s="18">
         <v>12617802</v>
       </c>
-      <c r="G2" s="16"/>
+      <c r="G2" s="18"/>
       <c r="H2" s="1"/>
       <c r="I2" s="1"/>
       <c r="J2" s="1"/>
@@ -671,18 +723,18 @@
       <c r="A3" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="B3" s="16" t="s">
+      <c r="B3" s="18" t="s">
         <v>21</v>
       </c>
-      <c r="C3" s="16"/>
-      <c r="D3" s="16"/>
+      <c r="C3" s="18"/>
+      <c r="D3" s="18"/>
       <c r="E3" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="F3" s="16" t="s">
+      <c r="F3" s="18" t="s">
         <v>22</v>
       </c>
-      <c r="G3" s="16"/>
+      <c r="G3" s="18"/>
       <c r="H3" s="1"/>
       <c r="I3" s="1"/>
       <c r="J3" s="1"/>
@@ -692,22 +744,22 @@
       <c r="N3" s="1"/>
     </row>
     <row r="4" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A4" s="14" t="s">
+      <c r="A4" s="16" t="s">
         <v>5</v>
       </c>
-      <c r="B4" s="14"/>
-      <c r="C4" s="14"/>
-      <c r="D4" s="14"/>
-      <c r="E4" s="14"/>
-      <c r="F4" s="14"/>
-      <c r="G4" s="14"/>
-      <c r="H4" s="14"/>
-      <c r="I4" s="14"/>
-      <c r="J4" s="14"/>
-      <c r="K4" s="14"/>
-      <c r="L4" s="14"/>
-      <c r="M4" s="14"/>
-      <c r="N4" s="14"/>
+      <c r="B4" s="16"/>
+      <c r="C4" s="16"/>
+      <c r="D4" s="16"/>
+      <c r="E4" s="16"/>
+      <c r="F4" s="16"/>
+      <c r="G4" s="16"/>
+      <c r="H4" s="16"/>
+      <c r="I4" s="16"/>
+      <c r="J4" s="16"/>
+      <c r="K4" s="16"/>
+      <c r="L4" s="16"/>
+      <c r="M4" s="16"/>
+      <c r="N4" s="16"/>
     </row>
     <row r="5" spans="1:14" ht="52.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="3" t="s">
@@ -1215,7 +1267,7 @@
       </c>
       <c r="N16" s="10"/>
     </row>
-    <row r="17" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A17" s="12">
         <v>46257</v>
       </c>
@@ -1257,8 +1309,8 @@
       </c>
       <c r="N17" s="10"/>
     </row>
-    <row r="18" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A18" s="12">
+    <row r="18" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A18" s="19">
         <v>46258</v>
       </c>
       <c r="B18" s="10">
@@ -1297,53 +1349,144 @@
       <c r="M18" s="10" t="s">
         <v>29</v>
       </c>
-      <c r="N18" s="10"/>
-    </row>
-    <row r="20" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A20" s="5"/>
-      <c r="B20" s="6"/>
-      <c r="C20" s="6"/>
-      <c r="D20" s="6"/>
-      <c r="E20" s="6"/>
-      <c r="F20" s="6"/>
-      <c r="G20" s="6"/>
-      <c r="H20" s="6"/>
-      <c r="I20" s="4" t="str">
-        <f t="shared" ref="I20:I44" si="0">IF(SUM(B20:F20,H20)=0,"",SUM(B20:F20,H20))</f>
-        <v/>
-      </c>
-      <c r="J20" s="4" t="str">
-        <f t="shared" ref="J20:J44" si="1">IF(I20="","",1440-I20)</f>
-        <v/>
-      </c>
-      <c r="K20" s="7"/>
-      <c r="L20" s="7"/>
-      <c r="M20" s="7"/>
-      <c r="N20" s="8"/>
-    </row>
-    <row r="21" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A21" s="5"/>
-      <c r="B21" s="6"/>
-      <c r="C21" s="6"/>
-      <c r="D21" s="6"/>
-      <c r="E21" s="6"/>
-      <c r="F21" s="6"/>
-      <c r="G21" s="6"/>
-      <c r="H21" s="6"/>
-      <c r="I21" s="4" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J21" s="4" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K21" s="7"/>
-      <c r="L21" s="7"/>
-      <c r="M21" s="7"/>
-      <c r="N21" s="8"/>
-    </row>
-    <row r="22" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="N18" t="s">
+        <v>36</v>
+      </c>
+      <c r="O18" s="10"/>
+    </row>
+    <row r="19" spans="1:15" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A19" s="12">
+        <v>46259</v>
+      </c>
+      <c r="B19" s="10">
+        <v>360</v>
+      </c>
+      <c r="C19" s="10">
+        <v>30</v>
+      </c>
+      <c r="D19" s="10">
+        <v>120</v>
+      </c>
+      <c r="E19" s="10">
+        <v>120</v>
+      </c>
+      <c r="F19" s="10">
+        <v>350</v>
+      </c>
+      <c r="G19" s="10">
+        <v>7</v>
+      </c>
+      <c r="H19" s="10">
+        <v>360</v>
+      </c>
+      <c r="I19" s="10">
+        <v>1340</v>
+      </c>
+      <c r="J19" s="10">
+        <v>100</v>
+      </c>
+      <c r="K19" s="10" t="s">
+        <v>34</v>
+      </c>
+      <c r="L19" s="10" t="s">
+        <v>20</v>
+      </c>
+      <c r="M19" s="10" t="s">
+        <v>29</v>
+      </c>
+      <c r="N19" s="10" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="20" spans="1:15" ht="13.2" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A20" s="12">
+        <v>46260</v>
+      </c>
+      <c r="B20" s="15">
+        <v>360</v>
+      </c>
+      <c r="C20" s="20">
+        <v>45</v>
+      </c>
+      <c r="D20" s="20">
+        <v>150</v>
+      </c>
+      <c r="E20" s="20">
+        <v>150</v>
+      </c>
+      <c r="F20" s="20">
+        <v>200</v>
+      </c>
+      <c r="G20" s="20">
+        <v>4</v>
+      </c>
+      <c r="H20" s="20">
+        <v>240</v>
+      </c>
+      <c r="I20" s="20">
+        <v>1145</v>
+      </c>
+      <c r="J20" s="20">
+        <v>295</v>
+      </c>
+      <c r="K20" s="20" t="s">
+        <v>25</v>
+      </c>
+      <c r="L20" s="20" t="s">
+        <v>20</v>
+      </c>
+      <c r="M20" s="20" t="s">
+        <v>26</v>
+      </c>
+      <c r="N20" s="14" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="21" spans="1:15" ht="13.8" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A21" s="12">
+        <v>46261</v>
+      </c>
+      <c r="B21" s="21">
+        <v>360</v>
+      </c>
+      <c r="C21" s="21">
+        <v>30</v>
+      </c>
+      <c r="D21" s="21">
+        <v>90</v>
+      </c>
+      <c r="E21" s="21">
+        <v>120</v>
+      </c>
+      <c r="F21" s="21">
+        <v>400</v>
+      </c>
+      <c r="G21" s="21">
+        <v>8</v>
+      </c>
+      <c r="H21" s="21">
+        <v>300</v>
+      </c>
+      <c r="I21" s="21">
+        <v>1300</v>
+      </c>
+      <c r="J21" s="21">
+        <v>140</v>
+      </c>
+      <c r="K21" s="20" t="s">
+        <v>38</v>
+      </c>
+      <c r="L21" s="20" t="s">
+        <v>28</v>
+      </c>
+      <c r="M21" s="20" t="s">
+        <v>29</v>
+      </c>
+      <c r="N21" s="14" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="22" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A22" s="5"/>
       <c r="B22" s="6"/>
       <c r="C22" s="6"/>
@@ -1353,11 +1496,11 @@
       <c r="G22" s="6"/>
       <c r="H22" s="6"/>
       <c r="I22" s="4" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" ref="I22:I43" si="0">IF(SUM(B22:F22,H22)=0,"",SUM(B22:F22,H22))</f>
         <v/>
       </c>
       <c r="J22" s="4" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" ref="J22:J43" si="1">IF(I22="","",1440-I22)</f>
         <v/>
       </c>
       <c r="K22" s="7"/>
@@ -1365,7 +1508,7 @@
       <c r="M22" s="7"/>
       <c r="N22" s="8"/>
     </row>
-    <row r="23" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A23" s="5"/>
       <c r="B23" s="6"/>
       <c r="C23" s="6"/>
@@ -1387,7 +1530,7 @@
       <c r="M23" s="7"/>
       <c r="N23" s="8"/>
     </row>
-    <row r="24" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A24" s="5"/>
       <c r="B24" s="6"/>
       <c r="C24" s="6"/>
@@ -1409,7 +1552,7 @@
       <c r="M24" s="7"/>
       <c r="N24" s="8"/>
     </row>
-    <row r="25" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A25" s="5"/>
       <c r="B25" s="6"/>
       <c r="C25" s="6"/>
@@ -1431,7 +1574,7 @@
       <c r="M25" s="7"/>
       <c r="N25" s="8"/>
     </row>
-    <row r="26" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A26" s="5"/>
       <c r="B26" s="6"/>
       <c r="C26" s="6"/>
@@ -1453,7 +1596,7 @@
       <c r="M26" s="7"/>
       <c r="N26" s="8"/>
     </row>
-    <row r="27" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A27" s="5"/>
       <c r="B27" s="6"/>
       <c r="C27" s="6"/>
@@ -1475,7 +1618,7 @@
       <c r="M27" s="7"/>
       <c r="N27" s="8"/>
     </row>
-    <row r="28" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A28" s="5"/>
       <c r="B28" s="6"/>
       <c r="C28" s="6"/>
@@ -1497,7 +1640,7 @@
       <c r="M28" s="7"/>
       <c r="N28" s="8"/>
     </row>
-    <row r="29" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A29" s="5"/>
       <c r="B29" s="6"/>
       <c r="C29" s="6"/>
@@ -1519,7 +1662,7 @@
       <c r="M29" s="7"/>
       <c r="N29" s="8"/>
     </row>
-    <row r="30" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A30" s="5"/>
       <c r="B30" s="6"/>
       <c r="C30" s="6"/>
@@ -1541,7 +1684,7 @@
       <c r="M30" s="7"/>
       <c r="N30" s="8"/>
     </row>
-    <row r="31" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A31" s="5"/>
       <c r="B31" s="6"/>
       <c r="C31" s="6"/>
@@ -1563,7 +1706,7 @@
       <c r="M31" s="7"/>
       <c r="N31" s="8"/>
     </row>
-    <row r="32" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A32" s="5"/>
       <c r="B32" s="6"/>
       <c r="C32" s="6"/>
@@ -1837,11 +1980,11 @@
       <c r="G44" s="6"/>
       <c r="H44" s="6"/>
       <c r="I44" s="4" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" ref="I44:I107" si="2">IF(SUM(B44:F44,H44)=0,"",SUM(B44:F44,H44))</f>
         <v/>
       </c>
       <c r="J44" s="4" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" ref="J44:J107" si="3">IF(I44="","",1440-I44)</f>
         <v/>
       </c>
       <c r="K44" s="7"/>
@@ -1859,11 +2002,11 @@
       <c r="G45" s="6"/>
       <c r="H45" s="6"/>
       <c r="I45" s="4" t="str">
-        <f t="shared" ref="I45:I108" si="2">IF(SUM(B45:F45,H45)=0,"",SUM(B45:F45,H45))</f>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="J45" s="4" t="str">
-        <f t="shared" ref="J45:J108" si="3">IF(I45="","",1440-I45)</f>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="K45" s="7"/>
@@ -3245,11 +3388,11 @@
       <c r="G108" s="6"/>
       <c r="H108" s="6"/>
       <c r="I108" s="4" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" ref="I108:I171" si="4">IF(SUM(B108:F108,H108)=0,"",SUM(B108:F108,H108))</f>
         <v/>
       </c>
       <c r="J108" s="4" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" ref="J108:J171" si="5">IF(I108="","",1440-I108)</f>
         <v/>
       </c>
       <c r="K108" s="7"/>
@@ -3267,11 +3410,11 @@
       <c r="G109" s="6"/>
       <c r="H109" s="6"/>
       <c r="I109" s="4" t="str">
-        <f t="shared" ref="I109:I172" si="4">IF(SUM(B109:F109,H109)=0,"",SUM(B109:F109,H109))</f>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J109" s="4" t="str">
-        <f t="shared" ref="J109:J172" si="5">IF(I109="","",1440-I109)</f>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K109" s="7"/>
@@ -4653,11 +4796,11 @@
       <c r="G172" s="6"/>
       <c r="H172" s="6"/>
       <c r="I172" s="4" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" ref="I172:I235" si="6">IF(SUM(B172:F172,H172)=0,"",SUM(B172:F172,H172))</f>
         <v/>
       </c>
       <c r="J172" s="4" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" ref="J172:J235" si="7">IF(I172="","",1440-I172)</f>
         <v/>
       </c>
       <c r="K172" s="7"/>
@@ -4675,11 +4818,11 @@
       <c r="G173" s="6"/>
       <c r="H173" s="6"/>
       <c r="I173" s="4" t="str">
-        <f t="shared" ref="I173:I236" si="6">IF(SUM(B173:F173,H173)=0,"",SUM(B173:F173,H173))</f>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J173" s="4" t="str">
-        <f t="shared" ref="J173:J236" si="7">IF(I173="","",1440-I173)</f>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K173" s="7"/>
@@ -6061,11 +6204,11 @@
       <c r="G236" s="6"/>
       <c r="H236" s="6"/>
       <c r="I236" s="4" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" ref="I236:I299" si="8">IF(SUM(B236:F236,H236)=0,"",SUM(B236:F236,H236))</f>
         <v/>
       </c>
       <c r="J236" s="4" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" ref="J236:J299" si="9">IF(I236="","",1440-I236)</f>
         <v/>
       </c>
       <c r="K236" s="7"/>
@@ -6083,11 +6226,11 @@
       <c r="G237" s="6"/>
       <c r="H237" s="6"/>
       <c r="I237" s="4" t="str">
-        <f t="shared" ref="I237:I300" si="8">IF(SUM(B237:F237,H237)=0,"",SUM(B237:F237,H237))</f>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J237" s="4" t="str">
-        <f t="shared" ref="J237:J300" si="9">IF(I237="","",1440-I237)</f>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K237" s="7"/>
@@ -7469,11 +7612,11 @@
       <c r="G300" s="6"/>
       <c r="H300" s="6"/>
       <c r="I300" s="4" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" ref="I300:I363" si="10">IF(SUM(B300:F300,H300)=0,"",SUM(B300:F300,H300))</f>
         <v/>
       </c>
       <c r="J300" s="4" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" ref="J300:J363" si="11">IF(I300="","",1440-I300)</f>
         <v/>
       </c>
       <c r="K300" s="7"/>
@@ -7491,11 +7634,11 @@
       <c r="G301" s="6"/>
       <c r="H301" s="6"/>
       <c r="I301" s="4" t="str">
-        <f t="shared" ref="I301:I364" si="10">IF(SUM(B301:F301,H301)=0,"",SUM(B301:F301,H301))</f>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J301" s="4" t="str">
-        <f t="shared" ref="J301:J364" si="11">IF(I301="","",1440-I301)</f>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K301" s="7"/>
@@ -8877,11 +9020,11 @@
       <c r="G364" s="6"/>
       <c r="H364" s="6"/>
       <c r="I364" s="4" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" ref="I364:I376" si="12">IF(SUM(B364:F364,H364)=0,"",SUM(B364:F364,H364))</f>
         <v/>
       </c>
       <c r="J364" s="4" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" ref="J364:J376" si="13">IF(I364="","",1440-I364)</f>
         <v/>
       </c>
       <c r="K364" s="7"/>
@@ -8899,11 +9042,11 @@
       <c r="G365" s="6"/>
       <c r="H365" s="6"/>
       <c r="I365" s="4" t="str">
-        <f t="shared" ref="I365:I377" si="12">IF(SUM(B365:F365,H365)=0,"",SUM(B365:F365,H365))</f>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J365" s="4" t="str">
-        <f t="shared" ref="J365:J377" si="13">IF(I365="","",1440-I365)</f>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K365" s="7"/>
@@ -9110,14 +9253,6 @@
       <c r="N374" s="8"/>
     </row>
     <row r="375" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A375" s="5"/>
-      <c r="B375" s="6"/>
-      <c r="C375" s="6"/>
-      <c r="D375" s="6"/>
-      <c r="E375" s="6"/>
-      <c r="F375" s="6"/>
-      <c r="G375" s="6"/>
-      <c r="H375" s="6"/>
       <c r="I375" s="4" t="str">
         <f t="shared" si="12"/>
         <v/>
@@ -9126,10 +9261,6 @@
         <f t="shared" si="13"/>
         <v/>
       </c>
-      <c r="K375" s="7"/>
-      <c r="L375" s="7"/>
-      <c r="M375" s="7"/>
-      <c r="N375" s="8"/>
     </row>
     <row r="376" spans="1:14" x14ac:dyDescent="0.3">
       <c r="I376" s="4" t="str">
@@ -9137,16 +9268,6 @@
         <v/>
       </c>
       <c r="J376" s="4" t="str">
-        <f t="shared" si="13"/>
-        <v/>
-      </c>
-    </row>
-    <row r="377" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="I377" s="4" t="str">
-        <f t="shared" si="12"/>
-        <v/>
-      </c>
-      <c r="J377" s="4" t="str">
         <f t="shared" si="13"/>
         <v/>
       </c>

--- a/CAP776 (PYTHON).xlsx
+++ b/CAP776 (PYTHON).xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\palak\Downloads\776(clone)\776\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{51051FB3-5E3F-4E8D-AB35-96B05F7E0056}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AD38EA5C-259C-4D81-9202-A4DF70D9C6B8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{327CE7B2-1886-45B8-951C-28CB36CE6AAF}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="75" uniqueCount="40">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="96" uniqueCount="48">
   <si>
     <t>My Data, My Code — Daily Log</t>
   </si>
@@ -155,6 +155,30 @@
   <si>
     <t>Full lecture day with heavy travel schedule</t>
   </si>
+  <si>
+    <t>Joyful</t>
+  </si>
+  <si>
+    <t>Raksha Bandhan festival &amp; family time</t>
+  </si>
+  <si>
+    <t>Productive</t>
+  </si>
+  <si>
+    <t>University off; heavy self-study &amp; coding</t>
+  </si>
+  <si>
+    <t>Sunday holiday &amp; self-paced revision</t>
+  </si>
+  <si>
+    <t>Balanced</t>
+  </si>
+  <si>
+    <t>Light class schedule (2 lectures)</t>
+  </si>
+  <si>
+    <t>Full lecture schedule &amp; travel</t>
+  </si>
 </sst>
 </file>
 
@@ -163,7 +187,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="yyyy\-mm\-dd"/>
   </numFmts>
-  <fonts count="9" x14ac:knownFonts="1">
+  <fonts count="8" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -211,14 +235,6 @@
       <color rgb="FF808080"/>
       <name val="Arial"/>
       <charset val="1"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
@@ -290,7 +306,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="22">
+  <cellXfs count="26">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1" applyFont="1"/>
@@ -321,27 +337,39 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="14" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="5"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="14" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="5"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="1" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="14" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="1" fillId="2" borderId="1" xfId="1" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -658,7 +686,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6E7F1806-3D91-4029-8849-359DB02F0997}">
-  <dimension ref="A1:O376"/>
+  <dimension ref="A1:O375"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="15.21875" customWidth="1"/>
@@ -677,40 +705,40 @@
     <col min="14" max="14" width="28.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" ht="16.8" x14ac:dyDescent="0.3">
-      <c r="A1" s="17" t="s">
+    <row r="1" spans="1:15" ht="16.8" x14ac:dyDescent="0.3">
+      <c r="A1" s="16" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="17"/>
-      <c r="C1" s="17"/>
-      <c r="D1" s="17"/>
-      <c r="E1" s="17"/>
-      <c r="F1" s="17"/>
-      <c r="G1" s="17"/>
-      <c r="H1" s="17"/>
-      <c r="I1" s="17"/>
-      <c r="J1" s="17"/>
-      <c r="K1" s="17"/>
-      <c r="L1" s="17"/>
-      <c r="M1" s="17"/>
-      <c r="N1" s="17"/>
-    </row>
-    <row r="2" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="B1" s="16"/>
+      <c r="C1" s="16"/>
+      <c r="D1" s="16"/>
+      <c r="E1" s="16"/>
+      <c r="F1" s="16"/>
+      <c r="G1" s="16"/>
+      <c r="H1" s="16"/>
+      <c r="I1" s="16"/>
+      <c r="J1" s="16"/>
+      <c r="K1" s="16"/>
+      <c r="L1" s="16"/>
+      <c r="M1" s="16"/>
+      <c r="N1" s="16"/>
+    </row>
+    <row r="2" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A2" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="18" t="s">
+      <c r="B2" s="17" t="s">
         <v>23</v>
       </c>
-      <c r="C2" s="18"/>
-      <c r="D2" s="18"/>
+      <c r="C2" s="17"/>
+      <c r="D2" s="17"/>
       <c r="E2" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="F2" s="18">
+      <c r="F2" s="17">
         <v>12617802</v>
       </c>
-      <c r="G2" s="18"/>
+      <c r="G2" s="17"/>
       <c r="H2" s="1"/>
       <c r="I2" s="1"/>
       <c r="J2" s="1"/>
@@ -719,22 +747,22 @@
       <c r="M2" s="1"/>
       <c r="N2" s="1"/>
     </row>
-    <row r="3" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A3" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="B3" s="18" t="s">
+      <c r="B3" s="17" t="s">
         <v>21</v>
       </c>
-      <c r="C3" s="18"/>
-      <c r="D3" s="18"/>
+      <c r="C3" s="17"/>
+      <c r="D3" s="17"/>
       <c r="E3" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="F3" s="18" t="s">
+      <c r="F3" s="17" t="s">
         <v>22</v>
       </c>
-      <c r="G3" s="18"/>
+      <c r="G3" s="17"/>
       <c r="H3" s="1"/>
       <c r="I3" s="1"/>
       <c r="J3" s="1"/>
@@ -743,25 +771,25 @@
       <c r="M3" s="1"/>
       <c r="N3" s="1"/>
     </row>
-    <row r="4" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A4" s="16" t="s">
+    <row r="4" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A4" s="15" t="s">
         <v>5</v>
       </c>
-      <c r="B4" s="16"/>
-      <c r="C4" s="16"/>
-      <c r="D4" s="16"/>
-      <c r="E4" s="16"/>
-      <c r="F4" s="16"/>
-      <c r="G4" s="16"/>
-      <c r="H4" s="16"/>
-      <c r="I4" s="16"/>
-      <c r="J4" s="16"/>
-      <c r="K4" s="16"/>
-      <c r="L4" s="16"/>
-      <c r="M4" s="16"/>
-      <c r="N4" s="16"/>
-    </row>
-    <row r="5" spans="1:14" ht="52.2" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B4" s="15"/>
+      <c r="C4" s="15"/>
+      <c r="D4" s="15"/>
+      <c r="E4" s="15"/>
+      <c r="F4" s="15"/>
+      <c r="G4" s="15"/>
+      <c r="H4" s="15"/>
+      <c r="I4" s="15"/>
+      <c r="J4" s="15"/>
+      <c r="K4" s="15"/>
+      <c r="L4" s="15"/>
+      <c r="M4" s="15"/>
+      <c r="N4" s="15"/>
+    </row>
+    <row r="5" spans="1:15" ht="52.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="3" t="s">
         <v>6</v>
       </c>
@@ -804,9 +832,12 @@
       <c r="N5" s="3" t="s">
         <v>19</v>
       </c>
-    </row>
-    <row r="6" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A6" s="12">
+      <c r="O5" s="3" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="6" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A6" s="18">
         <v>46246</v>
       </c>
       <c r="B6" s="9">
@@ -847,8 +878,8 @@
       </c>
       <c r="N6" s="8"/>
     </row>
-    <row r="7" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A7" s="12">
+    <row r="7" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A7" s="18">
         <v>46247</v>
       </c>
       <c r="B7" s="9">
@@ -889,8 +920,8 @@
       </c>
       <c r="N7" s="8"/>
     </row>
-    <row r="8" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A8" s="12">
+    <row r="8" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A8" s="18">
         <v>46248</v>
       </c>
       <c r="B8" s="9">
@@ -931,8 +962,8 @@
       </c>
       <c r="N8" s="8"/>
     </row>
-    <row r="9" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A9" s="13">
+    <row r="9" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A9" s="19">
         <v>46249</v>
       </c>
       <c r="B9" s="9">
@@ -973,8 +1004,8 @@
       </c>
       <c r="N9" s="8"/>
     </row>
-    <row r="10" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A10" s="12">
+    <row r="10" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A10" s="18">
         <v>46250</v>
       </c>
       <c r="B10" s="9">
@@ -1015,8 +1046,8 @@
       </c>
       <c r="N10" s="8"/>
     </row>
-    <row r="11" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A11" s="12">
+    <row r="11" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A11" s="18">
         <v>46251</v>
       </c>
       <c r="B11" s="10">
@@ -1057,8 +1088,8 @@
       </c>
       <c r="N11" s="10"/>
     </row>
-    <row r="12" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A12" s="12">
+    <row r="12" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A12" s="18">
         <v>46252</v>
       </c>
       <c r="B12" s="10">
@@ -1099,8 +1130,8 @@
       </c>
       <c r="N12" s="10"/>
     </row>
-    <row r="13" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A13" s="12">
+    <row r="13" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A13" s="18">
         <v>46253</v>
       </c>
       <c r="B13" s="10">
@@ -1141,8 +1172,8 @@
       </c>
       <c r="N13" s="10"/>
     </row>
-    <row r="14" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A14" s="12">
+    <row r="14" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A14" s="18">
         <v>46254</v>
       </c>
       <c r="B14" s="10">
@@ -1183,8 +1214,8 @@
       </c>
       <c r="N14" s="10"/>
     </row>
-    <row r="15" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A15" s="12">
+    <row r="15" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A15" s="18">
         <v>46255</v>
       </c>
       <c r="B15" s="10">
@@ -1225,8 +1256,8 @@
       </c>
       <c r="N15" s="10"/>
     </row>
-    <row r="16" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A16" s="12">
+    <row r="16" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A16" s="18">
         <v>46256</v>
       </c>
       <c r="B16" s="10">
@@ -1268,7 +1299,7 @@
       <c r="N16" s="10"/>
     </row>
     <row r="17" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A17" s="12">
+      <c r="A17" s="18">
         <v>46257</v>
       </c>
       <c r="B17" s="10">
@@ -1310,7 +1341,7 @@
       <c r="N17" s="10"/>
     </row>
     <row r="18" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A18" s="19">
+      <c r="A18" s="20">
         <v>46258</v>
       </c>
       <c r="B18" s="10">
@@ -1355,7 +1386,7 @@
       <c r="O18" s="10"/>
     </row>
     <row r="19" spans="1:15" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A19" s="12">
+      <c r="A19" s="18">
         <v>46259</v>
       </c>
       <c r="B19" s="10">
@@ -1399,206 +1430,316 @@
       </c>
     </row>
     <row r="20" spans="1:15" ht="13.2" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A20" s="12">
+      <c r="A20" s="18">
         <v>46260</v>
       </c>
-      <c r="B20" s="15">
+      <c r="B20" s="12">
         <v>360</v>
       </c>
-      <c r="C20" s="20">
+      <c r="C20" s="13">
         <v>45</v>
       </c>
-      <c r="D20" s="20">
+      <c r="D20" s="13">
         <v>150</v>
       </c>
-      <c r="E20" s="20">
+      <c r="E20" s="13">
         <v>150</v>
       </c>
-      <c r="F20" s="20">
+      <c r="F20" s="13">
         <v>200</v>
       </c>
-      <c r="G20" s="20">
+      <c r="G20" s="13">
         <v>4</v>
       </c>
-      <c r="H20" s="20">
+      <c r="H20" s="13">
         <v>240</v>
       </c>
-      <c r="I20" s="20">
+      <c r="I20" s="13">
         <v>1145</v>
       </c>
-      <c r="J20" s="20">
+      <c r="J20" s="13">
         <v>295</v>
       </c>
-      <c r="K20" s="20" t="s">
+      <c r="K20" s="13" t="s">
         <v>25</v>
       </c>
-      <c r="L20" s="20" t="s">
+      <c r="L20" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="M20" s="20" t="s">
+      <c r="M20" s="13" t="s">
         <v>26</v>
       </c>
-      <c r="N20" s="14" t="s">
+      <c r="N20" s="13" t="s">
         <v>37</v>
       </c>
     </row>
     <row r="21" spans="1:15" ht="13.8" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A21" s="12">
+      <c r="A21" s="18">
         <v>46261</v>
       </c>
-      <c r="B21" s="21">
+      <c r="B21" s="14">
         <v>360</v>
       </c>
-      <c r="C21" s="21">
+      <c r="C21" s="14">
         <v>30</v>
       </c>
-      <c r="D21" s="21">
+      <c r="D21" s="14">
         <v>90</v>
       </c>
-      <c r="E21" s="21">
+      <c r="E21" s="14">
         <v>120</v>
       </c>
-      <c r="F21" s="21">
+      <c r="F21" s="14">
         <v>400</v>
       </c>
-      <c r="G21" s="21">
+      <c r="G21" s="14">
         <v>8</v>
       </c>
-      <c r="H21" s="21">
+      <c r="H21" s="14">
         <v>300</v>
       </c>
-      <c r="I21" s="21">
+      <c r="I21" s="14">
         <v>1300</v>
       </c>
-      <c r="J21" s="21">
+      <c r="J21" s="14">
         <v>140</v>
       </c>
-      <c r="K21" s="20" t="s">
+      <c r="K21" s="13" t="s">
         <v>38</v>
       </c>
-      <c r="L21" s="20" t="s">
+      <c r="L21" s="13" t="s">
         <v>28</v>
       </c>
-      <c r="M21" s="20" t="s">
+      <c r="M21" s="13" t="s">
         <v>29</v>
       </c>
-      <c r="N21" s="14" t="s">
+      <c r="N21" s="13" t="s">
         <v>39</v>
       </c>
     </row>
-    <row r="22" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A22" s="5"/>
-      <c r="B22" s="6"/>
-      <c r="C22" s="6"/>
-      <c r="D22" s="6"/>
-      <c r="E22" s="6"/>
-      <c r="F22" s="6"/>
-      <c r="G22" s="6"/>
-      <c r="H22" s="6"/>
-      <c r="I22" s="4" t="str">
-        <f t="shared" ref="I22:I43" si="0">IF(SUM(B22:F22,H22)=0,"",SUM(B22:F22,H22))</f>
-        <v/>
-      </c>
-      <c r="J22" s="4" t="str">
-        <f t="shared" ref="J22:J43" si="1">IF(I22="","",1440-I22)</f>
-        <v/>
-      </c>
-      <c r="K22" s="7"/>
-      <c r="L22" s="7"/>
-      <c r="M22" s="7"/>
-      <c r="N22" s="8"/>
-    </row>
-    <row r="23" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A23" s="5"/>
-      <c r="B23" s="6"/>
-      <c r="C23" s="6"/>
-      <c r="D23" s="6"/>
-      <c r="E23" s="6"/>
-      <c r="F23" s="6"/>
-      <c r="G23" s="6"/>
-      <c r="H23" s="6"/>
-      <c r="I23" s="4" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J23" s="4" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K23" s="7"/>
-      <c r="L23" s="7"/>
-      <c r="M23" s="7"/>
-      <c r="N23" s="8"/>
-    </row>
-    <row r="24" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A24" s="5"/>
-      <c r="B24" s="6"/>
-      <c r="C24" s="6"/>
-      <c r="D24" s="6"/>
-      <c r="E24" s="6"/>
-      <c r="F24" s="6"/>
-      <c r="G24" s="6"/>
-      <c r="H24" s="6"/>
-      <c r="I24" s="4" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J24" s="4" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K24" s="7"/>
-      <c r="L24" s="7"/>
-      <c r="M24" s="7"/>
-      <c r="N24" s="8"/>
-    </row>
-    <row r="25" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A25" s="5"/>
-      <c r="B25" s="6"/>
-      <c r="C25" s="6"/>
-      <c r="D25" s="6"/>
-      <c r="E25" s="6"/>
-      <c r="F25" s="6"/>
-      <c r="G25" s="6"/>
-      <c r="H25" s="6"/>
-      <c r="I25" s="4" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J25" s="4" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K25" s="7"/>
-      <c r="L25" s="7"/>
-      <c r="M25" s="7"/>
-      <c r="N25" s="8"/>
-    </row>
-    <row r="26" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A26" s="5"/>
-      <c r="B26" s="6"/>
-      <c r="C26" s="6"/>
-      <c r="D26" s="6"/>
-      <c r="E26" s="6"/>
-      <c r="F26" s="6"/>
-      <c r="G26" s="6"/>
-      <c r="H26" s="6"/>
-      <c r="I26" s="4" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J26" s="4" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K26" s="7"/>
-      <c r="L26" s="7"/>
-      <c r="M26" s="7"/>
-      <c r="N26" s="8"/>
+    <row r="22" spans="1:15" ht="13.2" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A22" s="21">
+        <v>46262</v>
+      </c>
+      <c r="B22" s="22">
+        <v>420</v>
+      </c>
+      <c r="C22" s="13">
+        <v>45</v>
+      </c>
+      <c r="D22" s="13">
+        <v>180</v>
+      </c>
+      <c r="E22" s="13">
+        <v>180</v>
+      </c>
+      <c r="F22" s="24">
+        <v>0</v>
+      </c>
+      <c r="G22" s="13">
+        <v>0</v>
+      </c>
+      <c r="H22" s="13">
+        <v>300</v>
+      </c>
+      <c r="I22" s="13">
+        <v>1125</v>
+      </c>
+      <c r="J22" s="13">
+        <v>315</v>
+      </c>
+      <c r="K22" s="13" t="s">
+        <v>40</v>
+      </c>
+      <c r="L22" s="13" t="s">
+        <v>30</v>
+      </c>
+      <c r="M22" s="13" t="s">
+        <v>26</v>
+      </c>
+      <c r="N22" s="13" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="23" spans="1:15" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A23" s="21">
+        <v>46263</v>
+      </c>
+      <c r="B23" s="22">
+        <v>450</v>
+      </c>
+      <c r="C23" s="13">
+        <v>60</v>
+      </c>
+      <c r="D23" s="13">
+        <v>210</v>
+      </c>
+      <c r="E23" s="13">
+        <v>240</v>
+      </c>
+      <c r="F23" s="24">
+        <v>0</v>
+      </c>
+      <c r="G23" s="13">
+        <v>0</v>
+      </c>
+      <c r="H23" s="13">
+        <v>240</v>
+      </c>
+      <c r="I23" s="13">
+        <v>1200</v>
+      </c>
+      <c r="J23" s="13">
+        <v>240</v>
+      </c>
+      <c r="K23" s="13" t="s">
+        <v>42</v>
+      </c>
+      <c r="L23" s="13" t="s">
+        <v>30</v>
+      </c>
+      <c r="M23" s="13" t="s">
+        <v>26</v>
+      </c>
+      <c r="N23" s="13" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="24" spans="1:15" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A24" s="21">
+        <v>46264</v>
+      </c>
+      <c r="B24" s="22">
+        <v>480</v>
+      </c>
+      <c r="C24" s="13">
+        <v>60</v>
+      </c>
+      <c r="D24" s="13">
+        <v>150</v>
+      </c>
+      <c r="E24" s="13">
+        <v>180</v>
+      </c>
+      <c r="F24" s="24">
+        <v>0</v>
+      </c>
+      <c r="G24" s="13">
+        <v>0</v>
+      </c>
+      <c r="H24" s="13">
+        <v>270</v>
+      </c>
+      <c r="I24" s="13">
+        <v>1140</v>
+      </c>
+      <c r="J24" s="13">
+        <v>300</v>
+      </c>
+      <c r="K24" s="13" t="s">
+        <v>33</v>
+      </c>
+      <c r="L24" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="M24" s="13" t="s">
+        <v>29</v>
+      </c>
+      <c r="N24" s="13" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="25" spans="1:15" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A25" s="21">
+        <v>46265</v>
+      </c>
+      <c r="B25" s="22">
+        <v>360</v>
+      </c>
+      <c r="C25" s="13">
+        <v>45</v>
+      </c>
+      <c r="D25" s="13">
+        <v>150</v>
+      </c>
+      <c r="E25" s="13">
+        <v>150</v>
+      </c>
+      <c r="F25" s="24">
+        <v>100</v>
+      </c>
+      <c r="G25" s="13">
+        <v>2</v>
+      </c>
+      <c r="H25" s="13">
+        <v>240</v>
+      </c>
+      <c r="I25" s="13">
+        <v>1045</v>
+      </c>
+      <c r="J25" s="13">
+        <v>395</v>
+      </c>
+      <c r="K25" s="13" t="s">
+        <v>45</v>
+      </c>
+      <c r="L25" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="M25" s="13" t="s">
+        <v>26</v>
+      </c>
+      <c r="N25" s="13" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="26" spans="1:15" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A26" s="21">
+        <v>46266</v>
+      </c>
+      <c r="B26" s="22">
+        <v>360</v>
+      </c>
+      <c r="C26" s="13">
+        <v>30</v>
+      </c>
+      <c r="D26" s="13">
+        <v>120</v>
+      </c>
+      <c r="E26" s="13">
+        <v>120</v>
+      </c>
+      <c r="F26" s="24">
+        <v>350</v>
+      </c>
+      <c r="G26" s="13">
+        <v>7</v>
+      </c>
+      <c r="H26" s="13">
+        <v>360</v>
+      </c>
+      <c r="I26" s="13">
+        <v>1340</v>
+      </c>
+      <c r="J26" s="13">
+        <v>100</v>
+      </c>
+      <c r="K26" s="13" t="s">
+        <v>34</v>
+      </c>
+      <c r="L26" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="M26" s="13" t="s">
+        <v>29</v>
+      </c>
+      <c r="N26" s="13" t="s">
+        <v>47</v>
+      </c>
     </row>
     <row r="27" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A27" s="5"/>
-      <c r="B27" s="6"/>
+      <c r="B27" s="23"/>
       <c r="C27" s="6"/>
       <c r="D27" s="6"/>
       <c r="E27" s="6"/>
@@ -1606,17 +1747,17 @@
       <c r="G27" s="6"/>
       <c r="H27" s="6"/>
       <c r="I27" s="4" t="str">
-        <f t="shared" si="0"/>
+        <f>IF(SUM(B27:F27,H27)=0,"",SUM(B27:F27,H27))</f>
         <v/>
       </c>
       <c r="J27" s="4" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" ref="J27:J42" si="0">IF(I27="","",1440-I27)</f>
         <v/>
       </c>
       <c r="K27" s="7"/>
       <c r="L27" s="7"/>
       <c r="M27" s="7"/>
-      <c r="N27" s="8"/>
+      <c r="N27" s="25"/>
     </row>
     <row r="28" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A28" s="5"/>
@@ -1628,11 +1769,11 @@
       <c r="G28" s="6"/>
       <c r="H28" s="6"/>
       <c r="I28" s="4" t="str">
+        <f t="shared" ref="I28:I42" si="1">IF(SUM(B28:F28,H28)=0,"",SUM(B28:F28,H28))</f>
+        <v/>
+      </c>
+      <c r="J28" s="4" t="str">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J28" s="4" t="str">
-        <f t="shared" si="1"/>
         <v/>
       </c>
       <c r="K28" s="7"/>
@@ -1650,11 +1791,11 @@
       <c r="G29" s="6"/>
       <c r="H29" s="6"/>
       <c r="I29" s="4" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="J29" s="4" t="str">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J29" s="4" t="str">
-        <f t="shared" si="1"/>
         <v/>
       </c>
       <c r="K29" s="7"/>
@@ -1672,11 +1813,11 @@
       <c r="G30" s="6"/>
       <c r="H30" s="6"/>
       <c r="I30" s="4" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="J30" s="4" t="str">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J30" s="4" t="str">
-        <f t="shared" si="1"/>
         <v/>
       </c>
       <c r="K30" s="7"/>
@@ -1694,11 +1835,11 @@
       <c r="G31" s="6"/>
       <c r="H31" s="6"/>
       <c r="I31" s="4" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="J31" s="4" t="str">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J31" s="4" t="str">
-        <f t="shared" si="1"/>
         <v/>
       </c>
       <c r="K31" s="7"/>
@@ -1716,11 +1857,11 @@
       <c r="G32" s="6"/>
       <c r="H32" s="6"/>
       <c r="I32" s="4" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="J32" s="4" t="str">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J32" s="4" t="str">
-        <f t="shared" si="1"/>
         <v/>
       </c>
       <c r="K32" s="7"/>
@@ -1738,11 +1879,11 @@
       <c r="G33" s="6"/>
       <c r="H33" s="6"/>
       <c r="I33" s="4" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="J33" s="4" t="str">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J33" s="4" t="str">
-        <f t="shared" si="1"/>
         <v/>
       </c>
       <c r="K33" s="7"/>
@@ -1760,11 +1901,11 @@
       <c r="G34" s="6"/>
       <c r="H34" s="6"/>
       <c r="I34" s="4" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="J34" s="4" t="str">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J34" s="4" t="str">
-        <f t="shared" si="1"/>
         <v/>
       </c>
       <c r="K34" s="7"/>
@@ -1782,11 +1923,11 @@
       <c r="G35" s="6"/>
       <c r="H35" s="6"/>
       <c r="I35" s="4" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="J35" s="4" t="str">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J35" s="4" t="str">
-        <f t="shared" si="1"/>
         <v/>
       </c>
       <c r="K35" s="7"/>
@@ -1804,11 +1945,11 @@
       <c r="G36" s="6"/>
       <c r="H36" s="6"/>
       <c r="I36" s="4" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="J36" s="4" t="str">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J36" s="4" t="str">
-        <f t="shared" si="1"/>
         <v/>
       </c>
       <c r="K36" s="7"/>
@@ -1826,11 +1967,11 @@
       <c r="G37" s="6"/>
       <c r="H37" s="6"/>
       <c r="I37" s="4" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="J37" s="4" t="str">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J37" s="4" t="str">
-        <f t="shared" si="1"/>
         <v/>
       </c>
       <c r="K37" s="7"/>
@@ -1848,11 +1989,11 @@
       <c r="G38" s="6"/>
       <c r="H38" s="6"/>
       <c r="I38" s="4" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="J38" s="4" t="str">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J38" s="4" t="str">
-        <f t="shared" si="1"/>
         <v/>
       </c>
       <c r="K38" s="7"/>
@@ -1870,11 +2011,11 @@
       <c r="G39" s="6"/>
       <c r="H39" s="6"/>
       <c r="I39" s="4" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="J39" s="4" t="str">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J39" s="4" t="str">
-        <f t="shared" si="1"/>
         <v/>
       </c>
       <c r="K39" s="7"/>
@@ -1892,11 +2033,11 @@
       <c r="G40" s="6"/>
       <c r="H40" s="6"/>
       <c r="I40" s="4" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="J40" s="4" t="str">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J40" s="4" t="str">
-        <f t="shared" si="1"/>
         <v/>
       </c>
       <c r="K40" s="7"/>
@@ -1914,11 +2055,11 @@
       <c r="G41" s="6"/>
       <c r="H41" s="6"/>
       <c r="I41" s="4" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="J41" s="4" t="str">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J41" s="4" t="str">
-        <f t="shared" si="1"/>
         <v/>
       </c>
       <c r="K41" s="7"/>
@@ -1936,11 +2077,11 @@
       <c r="G42" s="6"/>
       <c r="H42" s="6"/>
       <c r="I42" s="4" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="J42" s="4" t="str">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J42" s="4" t="str">
-        <f t="shared" si="1"/>
         <v/>
       </c>
       <c r="K42" s="7"/>
@@ -1958,11 +2099,11 @@
       <c r="G43" s="6"/>
       <c r="H43" s="6"/>
       <c r="I43" s="4" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" ref="I43:I106" si="2">IF(SUM(B43:F43,H43)=0,"",SUM(B43:F43,H43))</f>
         <v/>
       </c>
       <c r="J43" s="4" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" ref="J43:J106" si="3">IF(I43="","",1440-I43)</f>
         <v/>
       </c>
       <c r="K43" s="7"/>
@@ -1980,11 +2121,11 @@
       <c r="G44" s="6"/>
       <c r="H44" s="6"/>
       <c r="I44" s="4" t="str">
-        <f t="shared" ref="I44:I107" si="2">IF(SUM(B44:F44,H44)=0,"",SUM(B44:F44,H44))</f>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="J44" s="4" t="str">
-        <f t="shared" ref="J44:J107" si="3">IF(I44="","",1440-I44)</f>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="K44" s="7"/>
@@ -3366,11 +3507,11 @@
       <c r="G107" s="6"/>
       <c r="H107" s="6"/>
       <c r="I107" s="4" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" ref="I107:I170" si="4">IF(SUM(B107:F107,H107)=0,"",SUM(B107:F107,H107))</f>
         <v/>
       </c>
       <c r="J107" s="4" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" ref="J107:J170" si="5">IF(I107="","",1440-I107)</f>
         <v/>
       </c>
       <c r="K107" s="7"/>
@@ -3388,11 +3529,11 @@
       <c r="G108" s="6"/>
       <c r="H108" s="6"/>
       <c r="I108" s="4" t="str">
-        <f t="shared" ref="I108:I171" si="4">IF(SUM(B108:F108,H108)=0,"",SUM(B108:F108,H108))</f>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J108" s="4" t="str">
-        <f t="shared" ref="J108:J171" si="5">IF(I108="","",1440-I108)</f>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K108" s="7"/>
@@ -4774,11 +4915,11 @@
       <c r="G171" s="6"/>
       <c r="H171" s="6"/>
       <c r="I171" s="4" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" ref="I171:I234" si="6">IF(SUM(B171:F171,H171)=0,"",SUM(B171:F171,H171))</f>
         <v/>
       </c>
       <c r="J171" s="4" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" ref="J171:J234" si="7">IF(I171="","",1440-I171)</f>
         <v/>
       </c>
       <c r="K171" s="7"/>
@@ -4796,11 +4937,11 @@
       <c r="G172" s="6"/>
       <c r="H172" s="6"/>
       <c r="I172" s="4" t="str">
-        <f t="shared" ref="I172:I235" si="6">IF(SUM(B172:F172,H172)=0,"",SUM(B172:F172,H172))</f>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J172" s="4" t="str">
-        <f t="shared" ref="J172:J235" si="7">IF(I172="","",1440-I172)</f>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K172" s="7"/>
@@ -6182,11 +6323,11 @@
       <c r="G235" s="6"/>
       <c r="H235" s="6"/>
       <c r="I235" s="4" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" ref="I235:I298" si="8">IF(SUM(B235:F235,H235)=0,"",SUM(B235:F235,H235))</f>
         <v/>
       </c>
       <c r="J235" s="4" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" ref="J235:J298" si="9">IF(I235="","",1440-I235)</f>
         <v/>
       </c>
       <c r="K235" s="7"/>
@@ -6204,11 +6345,11 @@
       <c r="G236" s="6"/>
       <c r="H236" s="6"/>
       <c r="I236" s="4" t="str">
-        <f t="shared" ref="I236:I299" si="8">IF(SUM(B236:F236,H236)=0,"",SUM(B236:F236,H236))</f>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J236" s="4" t="str">
-        <f t="shared" ref="J236:J299" si="9">IF(I236="","",1440-I236)</f>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K236" s="7"/>
@@ -7590,11 +7731,11 @@
       <c r="G299" s="6"/>
       <c r="H299" s="6"/>
       <c r="I299" s="4" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" ref="I299:I362" si="10">IF(SUM(B299:F299,H299)=0,"",SUM(B299:F299,H299))</f>
         <v/>
       </c>
       <c r="J299" s="4" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" ref="J299:J362" si="11">IF(I299="","",1440-I299)</f>
         <v/>
       </c>
       <c r="K299" s="7"/>
@@ -7612,11 +7753,11 @@
       <c r="G300" s="6"/>
       <c r="H300" s="6"/>
       <c r="I300" s="4" t="str">
-        <f t="shared" ref="I300:I363" si="10">IF(SUM(B300:F300,H300)=0,"",SUM(B300:F300,H300))</f>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J300" s="4" t="str">
-        <f t="shared" ref="J300:J363" si="11">IF(I300="","",1440-I300)</f>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K300" s="7"/>
@@ -8998,11 +9139,11 @@
       <c r="G363" s="6"/>
       <c r="H363" s="6"/>
       <c r="I363" s="4" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" ref="I363:I375" si="12">IF(SUM(B363:F363,H363)=0,"",SUM(B363:F363,H363))</f>
         <v/>
       </c>
       <c r="J363" s="4" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" ref="J363:J375" si="13">IF(I363="","",1440-I363)</f>
         <v/>
       </c>
       <c r="K363" s="7"/>
@@ -9020,11 +9161,11 @@
       <c r="G364" s="6"/>
       <c r="H364" s="6"/>
       <c r="I364" s="4" t="str">
-        <f t="shared" ref="I364:I376" si="12">IF(SUM(B364:F364,H364)=0,"",SUM(B364:F364,H364))</f>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J364" s="4" t="str">
-        <f t="shared" ref="J364:J376" si="13">IF(I364="","",1440-I364)</f>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K364" s="7"/>
@@ -9231,14 +9372,6 @@
       <c r="N373" s="8"/>
     </row>
     <row r="374" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A374" s="5"/>
-      <c r="B374" s="6"/>
-      <c r="C374" s="6"/>
-      <c r="D374" s="6"/>
-      <c r="E374" s="6"/>
-      <c r="F374" s="6"/>
-      <c r="G374" s="6"/>
-      <c r="H374" s="6"/>
       <c r="I374" s="4" t="str">
         <f t="shared" si="12"/>
         <v/>
@@ -9247,10 +9380,6 @@
         <f t="shared" si="13"/>
         <v/>
       </c>
-      <c r="K374" s="7"/>
-      <c r="L374" s="7"/>
-      <c r="M374" s="7"/>
-      <c r="N374" s="8"/>
     </row>
     <row r="375" spans="1:14" x14ac:dyDescent="0.3">
       <c r="I375" s="4" t="str">
@@ -9258,16 +9387,6 @@
         <v/>
       </c>
       <c r="J375" s="4" t="str">
-        <f t="shared" si="13"/>
-        <v/>
-      </c>
-    </row>
-    <row r="376" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="I376" s="4" t="str">
-        <f t="shared" si="12"/>
-        <v/>
-      </c>
-      <c r="J376" s="4" t="str">
         <f t="shared" si="13"/>
         <v/>
       </c>

--- a/CAP776 (PYTHON).xlsx
+++ b/CAP776 (PYTHON).xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\palak\Downloads\776(clone)\776\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AD38EA5C-259C-4D81-9202-A4DF70D9C6B8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BA98F6CC-76BC-44E5-A984-0F1F6B5630FA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{327CE7B2-1886-45B8-951C-28CB36CE6AAF}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="96" uniqueCount="48">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="123" uniqueCount="64">
   <si>
     <t>My Data, My Code — Daily Log</t>
   </si>
@@ -179,6 +179,54 @@
   <si>
     <t>Full lecture schedule &amp; travel</t>
   </si>
+  <si>
+    <t>Attended 4 classes &amp; focused on coding practice</t>
+  </si>
+  <si>
+    <t>Full lecture schedule (7 classes) &amp; commute</t>
+  </si>
+  <si>
+    <t>Completed 7 classes &amp; daily coursework</t>
+  </si>
+  <si>
+    <t>Saturday off; dedicated to analytical skills prep &amp; self-study</t>
+  </si>
+  <si>
+    <t>Attended 4 lectures and practiced core concepts</t>
+  </si>
+  <si>
+    <t>Heavy lecture day (8 classes) &amp; revision</t>
+  </si>
+  <si>
+    <t>Attended 6 classes and completed study tasks</t>
+  </si>
+  <si>
+    <t>Independence Day holiday &amp; self-study</t>
+  </si>
+  <si>
+    <t>Sunday off; dedicated to coding practice</t>
+  </si>
+  <si>
+    <t>Attended 5 classes and worked on programming tasks</t>
+  </si>
+  <si>
+    <t>6 lectures attended with self-study sessions</t>
+  </si>
+  <si>
+    <t>Attended 4 classes &amp; focused on hands-on coding</t>
+  </si>
+  <si>
+    <t>Attended 5 lectures and completed assignment work</t>
+  </si>
+  <si>
+    <t>Completed 6 classes &amp; daily practice goals</t>
+  </si>
+  <si>
+    <t>Saturday off; focused coding practice &amp; revision</t>
+  </si>
+  <si>
+    <t>Sunday holiday; relaxed &amp; reviewed week's work</t>
+  </si>
 </sst>
 </file>
 
@@ -187,7 +235,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="yyyy\-mm\-dd"/>
   </numFmts>
-  <fonts count="8" x14ac:knownFonts="1">
+  <fonts count="9" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -239,6 +287,13 @@
     <font>
       <sz val="11"/>
       <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
       <name val="Arial"/>
       <family val="2"/>
     </font>
@@ -306,7 +361,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="26">
+  <cellXfs count="29">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1" applyFont="1"/>
@@ -346,23 +401,7 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="14" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="1" fontId="1" fillId="2" borderId="1" xfId="1" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -370,6 +409,29 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="14" fontId="7" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1"/>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -686,7 +748,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6E7F1806-3D91-4029-8849-359DB02F0997}">
-  <dimension ref="A1:O375"/>
+  <dimension ref="A1:O374"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="15.21875" customWidth="1"/>
@@ -702,43 +764,43 @@
     <col min="11" max="11" width="16.88671875" customWidth="1"/>
     <col min="12" max="12" width="16.109375" customWidth="1"/>
     <col min="13" max="13" width="16.88671875" customWidth="1"/>
-    <col min="14" max="14" width="28.6640625" customWidth="1"/>
+    <col min="14" max="14" width="61.21875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15" ht="16.8" x14ac:dyDescent="0.3">
-      <c r="A1" s="16" t="s">
+    <row r="1" spans="1:14" ht="16.8" x14ac:dyDescent="0.3">
+      <c r="A1" s="19" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="16"/>
-      <c r="C1" s="16"/>
-      <c r="D1" s="16"/>
-      <c r="E1" s="16"/>
-      <c r="F1" s="16"/>
-      <c r="G1" s="16"/>
-      <c r="H1" s="16"/>
-      <c r="I1" s="16"/>
-      <c r="J1" s="16"/>
-      <c r="K1" s="16"/>
-      <c r="L1" s="16"/>
-      <c r="M1" s="16"/>
-      <c r="N1" s="16"/>
-    </row>
-    <row r="2" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="B1" s="19"/>
+      <c r="C1" s="19"/>
+      <c r="D1" s="19"/>
+      <c r="E1" s="19"/>
+      <c r="F1" s="19"/>
+      <c r="G1" s="19"/>
+      <c r="H1" s="19"/>
+      <c r="I1" s="19"/>
+      <c r="J1" s="19"/>
+      <c r="K1" s="19"/>
+      <c r="L1" s="19"/>
+      <c r="M1" s="19"/>
+      <c r="N1" s="19"/>
+    </row>
+    <row r="2" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A2" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="17" t="s">
+      <c r="B2" s="20" t="s">
         <v>23</v>
       </c>
-      <c r="C2" s="17"/>
-      <c r="D2" s="17"/>
+      <c r="C2" s="20"/>
+      <c r="D2" s="20"/>
       <c r="E2" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="F2" s="17">
+      <c r="F2" s="20">
         <v>12617802</v>
       </c>
-      <c r="G2" s="17"/>
+      <c r="G2" s="20"/>
       <c r="H2" s="1"/>
       <c r="I2" s="1"/>
       <c r="J2" s="1"/>
@@ -747,22 +809,22 @@
       <c r="M2" s="1"/>
       <c r="N2" s="1"/>
     </row>
-    <row r="3" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A3" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="B3" s="17" t="s">
+      <c r="B3" s="20" t="s">
         <v>21</v>
       </c>
-      <c r="C3" s="17"/>
-      <c r="D3" s="17"/>
+      <c r="C3" s="20"/>
+      <c r="D3" s="20"/>
       <c r="E3" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="F3" s="17" t="s">
+      <c r="F3" s="20" t="s">
         <v>22</v>
       </c>
-      <c r="G3" s="17"/>
+      <c r="G3" s="20"/>
       <c r="H3" s="1"/>
       <c r="I3" s="1"/>
       <c r="J3" s="1"/>
@@ -771,25 +833,25 @@
       <c r="M3" s="1"/>
       <c r="N3" s="1"/>
     </row>
-    <row r="4" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A4" s="15" t="s">
+    <row r="4" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A4" s="18" t="s">
         <v>5</v>
       </c>
-      <c r="B4" s="15"/>
-      <c r="C4" s="15"/>
-      <c r="D4" s="15"/>
-      <c r="E4" s="15"/>
-      <c r="F4" s="15"/>
-      <c r="G4" s="15"/>
-      <c r="H4" s="15"/>
-      <c r="I4" s="15"/>
-      <c r="J4" s="15"/>
-      <c r="K4" s="15"/>
-      <c r="L4" s="15"/>
-      <c r="M4" s="15"/>
-      <c r="N4" s="15"/>
-    </row>
-    <row r="5" spans="1:15" ht="52.2" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B4" s="18"/>
+      <c r="C4" s="18"/>
+      <c r="D4" s="18"/>
+      <c r="E4" s="18"/>
+      <c r="F4" s="18"/>
+      <c r="G4" s="18"/>
+      <c r="H4" s="18"/>
+      <c r="I4" s="18"/>
+      <c r="J4" s="18"/>
+      <c r="K4" s="18"/>
+      <c r="L4" s="18"/>
+      <c r="M4" s="18"/>
+      <c r="N4" s="18"/>
+    </row>
+    <row r="5" spans="1:14" ht="52.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="3" t="s">
         <v>6</v>
       </c>
@@ -829,15 +891,12 @@
       <c r="M5" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="N5" s="3" t="s">
+      <c r="N5" s="27" t="s">
         <v>19</v>
       </c>
-      <c r="O5" s="3" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="6" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A6" s="18">
+    </row>
+    <row r="6" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A6" s="23">
         <v>46246</v>
       </c>
       <c r="B6" s="9">
@@ -876,10 +935,12 @@
       <c r="M6" s="10" t="s">
         <v>26</v>
       </c>
-      <c r="N6" s="8"/>
-    </row>
-    <row r="7" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A7" s="18">
+      <c r="N6" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="7" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A7" s="23">
         <v>46247</v>
       </c>
       <c r="B7" s="9">
@@ -918,10 +979,12 @@
       <c r="M7" s="10" t="s">
         <v>29</v>
       </c>
-      <c r="N7" s="8"/>
-    </row>
-    <row r="8" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A8" s="18">
+      <c r="N7" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="8" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A8" s="23">
         <v>46248</v>
       </c>
       <c r="B8" s="9">
@@ -960,10 +1023,12 @@
       <c r="M8" s="10" t="s">
         <v>29</v>
       </c>
-      <c r="N8" s="8"/>
-    </row>
-    <row r="9" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A9" s="19">
+      <c r="N8" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="9" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A9" s="23">
         <v>46249</v>
       </c>
       <c r="B9" s="9">
@@ -1002,10 +1067,12 @@
       <c r="M9" s="11" t="s">
         <v>26</v>
       </c>
-      <c r="N9" s="8"/>
-    </row>
-    <row r="10" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A10" s="18">
+      <c r="N9" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="10" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A10" s="23">
         <v>46250</v>
       </c>
       <c r="B10" s="9">
@@ -1044,10 +1111,12 @@
       <c r="M10" s="10" t="s">
         <v>24</v>
       </c>
-      <c r="N10" s="8"/>
-    </row>
-    <row r="11" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A11" s="18">
+      <c r="N10" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="11" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A11" s="23">
         <v>46251</v>
       </c>
       <c r="B11" s="10">
@@ -1086,10 +1155,12 @@
       <c r="M11" s="10" t="s">
         <v>26</v>
       </c>
-      <c r="N11" s="10"/>
-    </row>
-    <row r="12" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A12" s="18">
+      <c r="N11" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="12" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A12" s="23">
         <v>46252</v>
       </c>
       <c r="B12" s="10">
@@ -1128,10 +1199,12 @@
       <c r="M12" s="10" t="s">
         <v>29</v>
       </c>
-      <c r="N12" s="10"/>
-    </row>
-    <row r="13" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A13" s="18">
+      <c r="N12" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="13" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A13" s="23">
         <v>46253</v>
       </c>
       <c r="B13" s="10">
@@ -1170,10 +1243,12 @@
       <c r="M13" s="10" t="s">
         <v>26</v>
       </c>
-      <c r="N13" s="10"/>
-    </row>
-    <row r="14" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A14" s="18">
+      <c r="N13" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="14" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A14" s="23">
         <v>46254</v>
       </c>
       <c r="B14" s="10">
@@ -1212,10 +1287,12 @@
       <c r="M14" s="10" t="s">
         <v>31</v>
       </c>
-      <c r="N14" s="10"/>
-    </row>
-    <row r="15" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A15" s="18">
+      <c r="N14" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="15" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A15" s="23">
         <v>46255</v>
       </c>
       <c r="B15" s="10">
@@ -1254,10 +1331,12 @@
       <c r="M15" s="10" t="s">
         <v>29</v>
       </c>
-      <c r="N15" s="10"/>
-    </row>
-    <row r="16" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A16" s="18">
+      <c r="N15" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="16" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A16" s="23">
         <v>46256</v>
       </c>
       <c r="B16" s="10">
@@ -1296,10 +1375,12 @@
       <c r="M16" s="10" t="s">
         <v>26</v>
       </c>
-      <c r="N16" s="10"/>
+      <c r="N16" t="s">
+        <v>62</v>
+      </c>
     </row>
     <row r="17" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A17" s="18">
+      <c r="A17" s="23">
         <v>46257</v>
       </c>
       <c r="B17" s="10">
@@ -1338,10 +1419,13 @@
       <c r="M17" s="10" t="s">
         <v>29</v>
       </c>
-      <c r="N17" s="10"/>
+      <c r="N17" t="s">
+        <v>63</v>
+      </c>
+      <c r="O17" s="10"/>
     </row>
     <row r="18" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A18" s="20">
+      <c r="A18" s="24">
         <v>46258</v>
       </c>
       <c r="B18" s="10">
@@ -1383,10 +1467,9 @@
       <c r="N18" t="s">
         <v>36</v>
       </c>
-      <c r="O18" s="10"/>
     </row>
     <row r="19" spans="1:15" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A19" s="18">
+      <c r="A19" s="23">
         <v>46259</v>
       </c>
       <c r="B19" s="10">
@@ -1430,7 +1513,7 @@
       </c>
     </row>
     <row r="20" spans="1:15" ht="13.2" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A20" s="18">
+      <c r="A20" s="23">
         <v>46260</v>
       </c>
       <c r="B20" s="12">
@@ -1474,7 +1557,7 @@
       </c>
     </row>
     <row r="21" spans="1:15" ht="13.8" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A21" s="18">
+      <c r="A21" s="23">
         <v>46261</v>
       </c>
       <c r="B21" s="14">
@@ -1518,10 +1601,10 @@
       </c>
     </row>
     <row r="22" spans="1:15" ht="13.2" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A22" s="21">
+      <c r="A22" s="25">
         <v>46262</v>
       </c>
-      <c r="B22" s="22">
+      <c r="B22" s="15">
         <v>420</v>
       </c>
       <c r="C22" s="13">
@@ -1533,7 +1616,7 @@
       <c r="E22" s="13">
         <v>180</v>
       </c>
-      <c r="F22" s="24">
+      <c r="F22" s="16">
         <v>0</v>
       </c>
       <c r="G22" s="13">
@@ -1562,10 +1645,10 @@
       </c>
     </row>
     <row r="23" spans="1:15" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A23" s="21">
+      <c r="A23" s="25">
         <v>46263</v>
       </c>
-      <c r="B23" s="22">
+      <c r="B23" s="15">
         <v>450</v>
       </c>
       <c r="C23" s="13">
@@ -1577,7 +1660,7 @@
       <c r="E23" s="13">
         <v>240</v>
       </c>
-      <c r="F23" s="24">
+      <c r="F23" s="16">
         <v>0</v>
       </c>
       <c r="G23" s="13">
@@ -1606,10 +1689,10 @@
       </c>
     </row>
     <row r="24" spans="1:15" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A24" s="21">
+      <c r="A24" s="25">
         <v>46264</v>
       </c>
-      <c r="B24" s="22">
+      <c r="B24" s="15">
         <v>480</v>
       </c>
       <c r="C24" s="13">
@@ -1621,7 +1704,7 @@
       <c r="E24" s="13">
         <v>180</v>
       </c>
-      <c r="F24" s="24">
+      <c r="F24" s="16">
         <v>0</v>
       </c>
       <c r="G24" s="13">
@@ -1650,10 +1733,10 @@
       </c>
     </row>
     <row r="25" spans="1:15" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A25" s="21">
+      <c r="A25" s="25">
         <v>46265</v>
       </c>
-      <c r="B25" s="22">
+      <c r="B25" s="15">
         <v>360</v>
       </c>
       <c r="C25" s="13">
@@ -1665,7 +1748,7 @@
       <c r="E25" s="13">
         <v>150</v>
       </c>
-      <c r="F25" s="24">
+      <c r="F25" s="22">
         <v>100</v>
       </c>
       <c r="G25" s="13">
@@ -1694,10 +1777,10 @@
       </c>
     </row>
     <row r="26" spans="1:15" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A26" s="21">
+      <c r="A26" s="25">
         <v>46266</v>
       </c>
-      <c r="B26" s="22">
+      <c r="B26" s="15">
         <v>360</v>
       </c>
       <c r="C26" s="13">
@@ -1709,7 +1792,7 @@
       <c r="E26" s="13">
         <v>120</v>
       </c>
-      <c r="F26" s="24">
+      <c r="F26" s="22">
         <v>350</v>
       </c>
       <c r="G26" s="13">
@@ -1737,93 +1820,181 @@
         <v>47</v>
       </c>
     </row>
-    <row r="27" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A27" s="5"/>
-      <c r="B27" s="23"/>
-      <c r="C27" s="6"/>
-      <c r="D27" s="6"/>
-      <c r="E27" s="6"/>
-      <c r="F27" s="6"/>
-      <c r="G27" s="6"/>
-      <c r="H27" s="6"/>
-      <c r="I27" s="4" t="str">
-        <f>IF(SUM(B27:F27,H27)=0,"",SUM(B27:F27,H27))</f>
-        <v/>
-      </c>
-      <c r="J27" s="4" t="str">
-        <f t="shared" ref="J27:J42" si="0">IF(I27="","",1440-I27)</f>
-        <v/>
-      </c>
-      <c r="K27" s="7"/>
-      <c r="L27" s="7"/>
-      <c r="M27" s="7"/>
-      <c r="N27" s="25"/>
-    </row>
-    <row r="28" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A28" s="5"/>
-      <c r="B28" s="6"/>
-      <c r="C28" s="6"/>
-      <c r="D28" s="6"/>
-      <c r="E28" s="6"/>
-      <c r="F28" s="6"/>
-      <c r="G28" s="6"/>
-      <c r="H28" s="6"/>
-      <c r="I28" s="4" t="str">
-        <f t="shared" ref="I28:I42" si="1">IF(SUM(B28:F28,H28)=0,"",SUM(B28:F28,H28))</f>
-        <v/>
-      </c>
-      <c r="J28" s="4" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="K28" s="7"/>
-      <c r="L28" s="7"/>
-      <c r="M28" s="7"/>
-      <c r="N28" s="8"/>
-    </row>
-    <row r="29" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A29" s="5"/>
-      <c r="B29" s="6"/>
-      <c r="C29" s="6"/>
-      <c r="D29" s="6"/>
-      <c r="E29" s="6"/>
-      <c r="F29" s="6"/>
-      <c r="G29" s="6"/>
-      <c r="H29" s="6"/>
-      <c r="I29" s="4" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="J29" s="4" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="K29" s="7"/>
-      <c r="L29" s="7"/>
-      <c r="M29" s="7"/>
-      <c r="N29" s="8"/>
-    </row>
-    <row r="30" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A30" s="5"/>
-      <c r="B30" s="6"/>
-      <c r="C30" s="6"/>
-      <c r="D30" s="6"/>
-      <c r="E30" s="6"/>
-      <c r="F30" s="6"/>
-      <c r="G30" s="6"/>
-      <c r="H30" s="6"/>
-      <c r="I30" s="4" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="J30" s="4" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="K30" s="7"/>
-      <c r="L30" s="7"/>
-      <c r="M30" s="7"/>
-      <c r="N30" s="8"/>
+    <row r="27" spans="1:15" ht="15.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A27" s="21">
+        <v>46267</v>
+      </c>
+      <c r="B27" s="22">
+        <v>360</v>
+      </c>
+      <c r="C27" s="22">
+        <v>45</v>
+      </c>
+      <c r="D27" s="22">
+        <v>150</v>
+      </c>
+      <c r="E27" s="22">
+        <v>150</v>
+      </c>
+      <c r="F27" s="22">
+        <v>200</v>
+      </c>
+      <c r="G27" s="22">
+        <v>4</v>
+      </c>
+      <c r="H27" s="22">
+        <v>240</v>
+      </c>
+      <c r="I27" s="22">
+        <v>1145</v>
+      </c>
+      <c r="J27" s="22">
+        <v>295</v>
+      </c>
+      <c r="K27" s="13" t="s">
+        <v>25</v>
+      </c>
+      <c r="L27" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="M27" s="28" t="s">
+        <v>26</v>
+      </c>
+      <c r="N27" s="13" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="28" spans="1:15" ht="17.399999999999999" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A28" s="21">
+        <v>46268</v>
+      </c>
+      <c r="B28" s="22">
+        <v>360</v>
+      </c>
+      <c r="C28" s="22">
+        <v>30</v>
+      </c>
+      <c r="D28" s="22">
+        <v>120</v>
+      </c>
+      <c r="E28" s="22">
+        <v>120</v>
+      </c>
+      <c r="F28" s="22">
+        <v>350</v>
+      </c>
+      <c r="G28" s="22">
+        <v>7</v>
+      </c>
+      <c r="H28" s="22">
+        <v>360</v>
+      </c>
+      <c r="I28" s="22">
+        <v>1340</v>
+      </c>
+      <c r="J28" s="22">
+        <v>100</v>
+      </c>
+      <c r="K28" s="13" t="s">
+        <v>34</v>
+      </c>
+      <c r="L28" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="M28" s="28" t="s">
+        <v>29</v>
+      </c>
+      <c r="N28" s="13" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="29" spans="1:15" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A29" s="21">
+        <v>46269</v>
+      </c>
+      <c r="B29" s="22">
+        <v>360</v>
+      </c>
+      <c r="C29" s="22">
+        <v>30</v>
+      </c>
+      <c r="D29" s="22">
+        <v>120</v>
+      </c>
+      <c r="E29" s="22">
+        <v>120</v>
+      </c>
+      <c r="F29" s="22">
+        <v>350</v>
+      </c>
+      <c r="G29" s="22">
+        <v>7</v>
+      </c>
+      <c r="H29" s="22">
+        <v>360</v>
+      </c>
+      <c r="I29" s="22">
+        <v>1340</v>
+      </c>
+      <c r="J29" s="26">
+        <v>100</v>
+      </c>
+      <c r="K29" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="L29" s="13" t="s">
+        <v>29</v>
+      </c>
+      <c r="M29" s="28" t="s">
+        <v>29</v>
+      </c>
+      <c r="N29" s="13" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="30" spans="1:15" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A30" s="21">
+        <v>46270</v>
+      </c>
+      <c r="B30" s="22">
+        <v>450</v>
+      </c>
+      <c r="C30" s="22">
+        <v>60</v>
+      </c>
+      <c r="D30" s="22">
+        <v>240</v>
+      </c>
+      <c r="E30" s="22">
+        <v>210</v>
+      </c>
+      <c r="F30" s="22">
+        <v>0</v>
+      </c>
+      <c r="G30" s="22">
+        <v>0</v>
+      </c>
+      <c r="H30" s="22">
+        <v>240</v>
+      </c>
+      <c r="I30" s="22">
+        <v>1200</v>
+      </c>
+      <c r="J30" s="22">
+        <v>240</v>
+      </c>
+      <c r="K30" s="13" t="s">
+        <v>42</v>
+      </c>
+      <c r="L30" s="13" t="s">
+        <v>30</v>
+      </c>
+      <c r="M30" s="28" t="s">
+        <v>26</v>
+      </c>
+      <c r="N30" s="13" t="s">
+        <v>51</v>
+      </c>
     </row>
     <row r="31" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A31" s="5"/>
@@ -1835,17 +2006,17 @@
       <c r="G31" s="6"/>
       <c r="H31" s="6"/>
       <c r="I31" s="4" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" ref="I31:I41" si="0">IF(SUM(B31:F31,H31)=0,"",SUM(B31:F31,H31))</f>
         <v/>
       </c>
       <c r="J31" s="4" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" ref="J31:J41" si="1">IF(I31="","",1440-I31)</f>
         <v/>
       </c>
       <c r="K31" s="7"/>
       <c r="L31" s="7"/>
       <c r="M31" s="7"/>
-      <c r="N31" s="8"/>
+      <c r="N31" s="17"/>
     </row>
     <row r="32" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A32" s="5"/>
@@ -1857,11 +2028,11 @@
       <c r="G32" s="6"/>
       <c r="H32" s="6"/>
       <c r="I32" s="4" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="J32" s="4" t="str">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="J32" s="4" t="str">
-        <f t="shared" si="0"/>
         <v/>
       </c>
       <c r="K32" s="7"/>
@@ -1879,11 +2050,11 @@
       <c r="G33" s="6"/>
       <c r="H33" s="6"/>
       <c r="I33" s="4" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="J33" s="4" t="str">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="J33" s="4" t="str">
-        <f t="shared" si="0"/>
         <v/>
       </c>
       <c r="K33" s="7"/>
@@ -1901,11 +2072,11 @@
       <c r="G34" s="6"/>
       <c r="H34" s="6"/>
       <c r="I34" s="4" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="J34" s="4" t="str">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="J34" s="4" t="str">
-        <f t="shared" si="0"/>
         <v/>
       </c>
       <c r="K34" s="7"/>
@@ -1923,11 +2094,11 @@
       <c r="G35" s="6"/>
       <c r="H35" s="6"/>
       <c r="I35" s="4" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="J35" s="4" t="str">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="J35" s="4" t="str">
-        <f t="shared" si="0"/>
         <v/>
       </c>
       <c r="K35" s="7"/>
@@ -1945,11 +2116,11 @@
       <c r="G36" s="6"/>
       <c r="H36" s="6"/>
       <c r="I36" s="4" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="J36" s="4" t="str">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="J36" s="4" t="str">
-        <f t="shared" si="0"/>
         <v/>
       </c>
       <c r="K36" s="7"/>
@@ -1967,11 +2138,11 @@
       <c r="G37" s="6"/>
       <c r="H37" s="6"/>
       <c r="I37" s="4" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="J37" s="4" t="str">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="J37" s="4" t="str">
-        <f t="shared" si="0"/>
         <v/>
       </c>
       <c r="K37" s="7"/>
@@ -1989,11 +2160,11 @@
       <c r="G38" s="6"/>
       <c r="H38" s="6"/>
       <c r="I38" s="4" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="J38" s="4" t="str">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="J38" s="4" t="str">
-        <f t="shared" si="0"/>
         <v/>
       </c>
       <c r="K38" s="7"/>
@@ -2011,11 +2182,11 @@
       <c r="G39" s="6"/>
       <c r="H39" s="6"/>
       <c r="I39" s="4" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="J39" s="4" t="str">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="J39" s="4" t="str">
-        <f t="shared" si="0"/>
         <v/>
       </c>
       <c r="K39" s="7"/>
@@ -2033,11 +2204,11 @@
       <c r="G40" s="6"/>
       <c r="H40" s="6"/>
       <c r="I40" s="4" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="J40" s="4" t="str">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="J40" s="4" t="str">
-        <f t="shared" si="0"/>
         <v/>
       </c>
       <c r="K40" s="7"/>
@@ -2055,11 +2226,11 @@
       <c r="G41" s="6"/>
       <c r="H41" s="6"/>
       <c r="I41" s="4" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="J41" s="4" t="str">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="J41" s="4" t="str">
-        <f t="shared" si="0"/>
         <v/>
       </c>
       <c r="K41" s="7"/>
@@ -2077,11 +2248,11 @@
       <c r="G42" s="6"/>
       <c r="H42" s="6"/>
       <c r="I42" s="4" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" ref="I42:I105" si="2">IF(SUM(B42:F42,H42)=0,"",SUM(B42:F42,H42))</f>
         <v/>
       </c>
       <c r="J42" s="4" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" ref="J42:J105" si="3">IF(I42="","",1440-I42)</f>
         <v/>
       </c>
       <c r="K42" s="7"/>
@@ -2099,11 +2270,11 @@
       <c r="G43" s="6"/>
       <c r="H43" s="6"/>
       <c r="I43" s="4" t="str">
-        <f t="shared" ref="I43:I106" si="2">IF(SUM(B43:F43,H43)=0,"",SUM(B43:F43,H43))</f>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="J43" s="4" t="str">
-        <f t="shared" ref="J43:J106" si="3">IF(I43="","",1440-I43)</f>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="K43" s="7"/>
@@ -3485,11 +3656,11 @@
       <c r="G106" s="6"/>
       <c r="H106" s="6"/>
       <c r="I106" s="4" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" ref="I106:I169" si="4">IF(SUM(B106:F106,H106)=0,"",SUM(B106:F106,H106))</f>
         <v/>
       </c>
       <c r="J106" s="4" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" ref="J106:J169" si="5">IF(I106="","",1440-I106)</f>
         <v/>
       </c>
       <c r="K106" s="7"/>
@@ -3507,11 +3678,11 @@
       <c r="G107" s="6"/>
       <c r="H107" s="6"/>
       <c r="I107" s="4" t="str">
-        <f t="shared" ref="I107:I170" si="4">IF(SUM(B107:F107,H107)=0,"",SUM(B107:F107,H107))</f>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J107" s="4" t="str">
-        <f t="shared" ref="J107:J170" si="5">IF(I107="","",1440-I107)</f>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K107" s="7"/>
@@ -4893,11 +5064,11 @@
       <c r="G170" s="6"/>
       <c r="H170" s="6"/>
       <c r="I170" s="4" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" ref="I170:I233" si="6">IF(SUM(B170:F170,H170)=0,"",SUM(B170:F170,H170))</f>
         <v/>
       </c>
       <c r="J170" s="4" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" ref="J170:J233" si="7">IF(I170="","",1440-I170)</f>
         <v/>
       </c>
       <c r="K170" s="7"/>
@@ -4915,11 +5086,11 @@
       <c r="G171" s="6"/>
       <c r="H171" s="6"/>
       <c r="I171" s="4" t="str">
-        <f t="shared" ref="I171:I234" si="6">IF(SUM(B171:F171,H171)=0,"",SUM(B171:F171,H171))</f>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J171" s="4" t="str">
-        <f t="shared" ref="J171:J234" si="7">IF(I171="","",1440-I171)</f>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K171" s="7"/>
@@ -6301,11 +6472,11 @@
       <c r="G234" s="6"/>
       <c r="H234" s="6"/>
       <c r="I234" s="4" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" ref="I234:I297" si="8">IF(SUM(B234:F234,H234)=0,"",SUM(B234:F234,H234))</f>
         <v/>
       </c>
       <c r="J234" s="4" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" ref="J234:J297" si="9">IF(I234="","",1440-I234)</f>
         <v/>
       </c>
       <c r="K234" s="7"/>
@@ -6323,11 +6494,11 @@
       <c r="G235" s="6"/>
       <c r="H235" s="6"/>
       <c r="I235" s="4" t="str">
-        <f t="shared" ref="I235:I298" si="8">IF(SUM(B235:F235,H235)=0,"",SUM(B235:F235,H235))</f>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J235" s="4" t="str">
-        <f t="shared" ref="J235:J298" si="9">IF(I235="","",1440-I235)</f>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K235" s="7"/>
@@ -7709,11 +7880,11 @@
       <c r="G298" s="6"/>
       <c r="H298" s="6"/>
       <c r="I298" s="4" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" ref="I298:I361" si="10">IF(SUM(B298:F298,H298)=0,"",SUM(B298:F298,H298))</f>
         <v/>
       </c>
       <c r="J298" s="4" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" ref="J298:J361" si="11">IF(I298="","",1440-I298)</f>
         <v/>
       </c>
       <c r="K298" s="7"/>
@@ -7731,11 +7902,11 @@
       <c r="G299" s="6"/>
       <c r="H299" s="6"/>
       <c r="I299" s="4" t="str">
-        <f t="shared" ref="I299:I362" si="10">IF(SUM(B299:F299,H299)=0,"",SUM(B299:F299,H299))</f>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J299" s="4" t="str">
-        <f t="shared" ref="J299:J362" si="11">IF(I299="","",1440-I299)</f>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K299" s="7"/>
@@ -9117,11 +9288,11 @@
       <c r="G362" s="6"/>
       <c r="H362" s="6"/>
       <c r="I362" s="4" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" ref="I362:I374" si="12">IF(SUM(B362:F362,H362)=0,"",SUM(B362:F362,H362))</f>
         <v/>
       </c>
       <c r="J362" s="4" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" ref="J362:J374" si="13">IF(I362="","",1440-I362)</f>
         <v/>
       </c>
       <c r="K362" s="7"/>
@@ -9139,11 +9310,11 @@
       <c r="G363" s="6"/>
       <c r="H363" s="6"/>
       <c r="I363" s="4" t="str">
-        <f t="shared" ref="I363:I375" si="12">IF(SUM(B363:F363,H363)=0,"",SUM(B363:F363,H363))</f>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J363" s="4" t="str">
-        <f t="shared" ref="J363:J375" si="13">IF(I363="","",1440-I363)</f>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K363" s="7"/>
@@ -9350,14 +9521,6 @@
       <c r="N372" s="8"/>
     </row>
     <row r="373" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A373" s="5"/>
-      <c r="B373" s="6"/>
-      <c r="C373" s="6"/>
-      <c r="D373" s="6"/>
-      <c r="E373" s="6"/>
-      <c r="F373" s="6"/>
-      <c r="G373" s="6"/>
-      <c r="H373" s="6"/>
       <c r="I373" s="4" t="str">
         <f t="shared" si="12"/>
         <v/>
@@ -9366,10 +9529,6 @@
         <f t="shared" si="13"/>
         <v/>
       </c>
-      <c r="K373" s="7"/>
-      <c r="L373" s="7"/>
-      <c r="M373" s="7"/>
-      <c r="N373" s="8"/>
     </row>
     <row r="374" spans="1:14" x14ac:dyDescent="0.3">
       <c r="I374" s="4" t="str">
@@ -9377,16 +9536,6 @@
         <v/>
       </c>
       <c r="J374" s="4" t="str">
-        <f t="shared" si="13"/>
-        <v/>
-      </c>
-    </row>
-    <row r="375" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="I375" s="4" t="str">
-        <f t="shared" si="12"/>
-        <v/>
-      </c>
-      <c r="J375" s="4" t="str">
         <f t="shared" si="13"/>
         <v/>
       </c>

--- a/CAP776 (PYTHON).xlsx
+++ b/CAP776 (PYTHON).xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\palak\Downloads\776(clone)\776\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BA98F6CC-76BC-44E5-A984-0F1F6B5630FA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2A5F7AD6-29CD-4941-AEAB-420C3F1BD014}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{327CE7B2-1886-45B8-951C-28CB36CE6AAF}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="123" uniqueCount="64">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="131" uniqueCount="66">
   <si>
     <t>My Data, My Code — Daily Log</t>
   </si>
@@ -227,6 +227,12 @@
   <si>
     <t>Sunday holiday; relaxed &amp; reviewed week's work</t>
   </si>
+  <si>
+    <t>Sunday off; dedicated full time to CA preparation</t>
+  </si>
+  <si>
+    <t>Woke up early at 4 AM for CA prep, attended 3 classes &amp; rested after home</t>
+  </si>
 </sst>
 </file>
 
@@ -361,7 +367,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="29">
+  <cellXfs count="27">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1" applyFont="1"/>
@@ -404,15 +410,6 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="14" fontId="7" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
@@ -422,16 +419,21 @@
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1"/>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="8" fillId="3" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="14" fontId="7" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -748,7 +750,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6E7F1806-3D91-4029-8849-359DB02F0997}">
-  <dimension ref="A1:O374"/>
+  <dimension ref="A1:O373"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="15.21875" customWidth="1"/>
@@ -768,39 +770,39 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:14" ht="16.8" x14ac:dyDescent="0.3">
-      <c r="A1" s="19" t="s">
+      <c r="A1" s="24" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="19"/>
-      <c r="C1" s="19"/>
-      <c r="D1" s="19"/>
-      <c r="E1" s="19"/>
-      <c r="F1" s="19"/>
-      <c r="G1" s="19"/>
-      <c r="H1" s="19"/>
-      <c r="I1" s="19"/>
-      <c r="J1" s="19"/>
-      <c r="K1" s="19"/>
-      <c r="L1" s="19"/>
-      <c r="M1" s="19"/>
-      <c r="N1" s="19"/>
+      <c r="B1" s="24"/>
+      <c r="C1" s="24"/>
+      <c r="D1" s="24"/>
+      <c r="E1" s="24"/>
+      <c r="F1" s="24"/>
+      <c r="G1" s="24"/>
+      <c r="H1" s="24"/>
+      <c r="I1" s="24"/>
+      <c r="J1" s="24"/>
+      <c r="K1" s="24"/>
+      <c r="L1" s="24"/>
+      <c r="M1" s="24"/>
+      <c r="N1" s="24"/>
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A2" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="20" t="s">
+      <c r="B2" s="25" t="s">
         <v>23</v>
       </c>
-      <c r="C2" s="20"/>
-      <c r="D2" s="20"/>
+      <c r="C2" s="25"/>
+      <c r="D2" s="25"/>
       <c r="E2" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="F2" s="20">
+      <c r="F2" s="25">
         <v>12617802</v>
       </c>
-      <c r="G2" s="20"/>
+      <c r="G2" s="25"/>
       <c r="H2" s="1"/>
       <c r="I2" s="1"/>
       <c r="J2" s="1"/>
@@ -813,18 +815,18 @@
       <c r="A3" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="B3" s="20" t="s">
+      <c r="B3" s="25" t="s">
         <v>21</v>
       </c>
-      <c r="C3" s="20"/>
-      <c r="D3" s="20"/>
+      <c r="C3" s="25"/>
+      <c r="D3" s="25"/>
       <c r="E3" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="F3" s="20" t="s">
+      <c r="F3" s="25" t="s">
         <v>22</v>
       </c>
-      <c r="G3" s="20"/>
+      <c r="G3" s="25"/>
       <c r="H3" s="1"/>
       <c r="I3" s="1"/>
       <c r="J3" s="1"/>
@@ -834,22 +836,22 @@
       <c r="N3" s="1"/>
     </row>
     <row r="4" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A4" s="18" t="s">
+      <c r="A4" s="23" t="s">
         <v>5</v>
       </c>
-      <c r="B4" s="18"/>
-      <c r="C4" s="18"/>
-      <c r="D4" s="18"/>
-      <c r="E4" s="18"/>
-      <c r="F4" s="18"/>
-      <c r="G4" s="18"/>
-      <c r="H4" s="18"/>
-      <c r="I4" s="18"/>
-      <c r="J4" s="18"/>
-      <c r="K4" s="18"/>
-      <c r="L4" s="18"/>
-      <c r="M4" s="18"/>
-      <c r="N4" s="18"/>
+      <c r="B4" s="23"/>
+      <c r="C4" s="23"/>
+      <c r="D4" s="23"/>
+      <c r="E4" s="23"/>
+      <c r="F4" s="23"/>
+      <c r="G4" s="23"/>
+      <c r="H4" s="23"/>
+      <c r="I4" s="23"/>
+      <c r="J4" s="23"/>
+      <c r="K4" s="23"/>
+      <c r="L4" s="23"/>
+      <c r="M4" s="23"/>
+      <c r="N4" s="23"/>
     </row>
     <row r="5" spans="1:14" ht="52.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="3" t="s">
@@ -891,12 +893,12 @@
       <c r="M5" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="N5" s="27" t="s">
+      <c r="N5" s="21" t="s">
         <v>19</v>
       </c>
     </row>
     <row r="6" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A6" s="23">
+      <c r="A6" s="18">
         <v>46246</v>
       </c>
       <c r="B6" s="9">
@@ -940,7 +942,7 @@
       </c>
     </row>
     <row r="7" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A7" s="23">
+      <c r="A7" s="18">
         <v>46247</v>
       </c>
       <c r="B7" s="9">
@@ -984,7 +986,7 @@
       </c>
     </row>
     <row r="8" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A8" s="23">
+      <c r="A8" s="18">
         <v>46248</v>
       </c>
       <c r="B8" s="9">
@@ -1028,7 +1030,7 @@
       </c>
     </row>
     <row r="9" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A9" s="23">
+      <c r="A9" s="18">
         <v>46249</v>
       </c>
       <c r="B9" s="9">
@@ -1072,7 +1074,7 @@
       </c>
     </row>
     <row r="10" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A10" s="23">
+      <c r="A10" s="18">
         <v>46250</v>
       </c>
       <c r="B10" s="9">
@@ -1116,7 +1118,7 @@
       </c>
     </row>
     <row r="11" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A11" s="23">
+      <c r="A11" s="18">
         <v>46251</v>
       </c>
       <c r="B11" s="10">
@@ -1160,7 +1162,7 @@
       </c>
     </row>
     <row r="12" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A12" s="23">
+      <c r="A12" s="18">
         <v>46252</v>
       </c>
       <c r="B12" s="10">
@@ -1204,7 +1206,7 @@
       </c>
     </row>
     <row r="13" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A13" s="23">
+      <c r="A13" s="18">
         <v>46253</v>
       </c>
       <c r="B13" s="10">
@@ -1248,7 +1250,7 @@
       </c>
     </row>
     <row r="14" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A14" s="23">
+      <c r="A14" s="18">
         <v>46254</v>
       </c>
       <c r="B14" s="10">
@@ -1292,7 +1294,7 @@
       </c>
     </row>
     <row r="15" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A15" s="23">
+      <c r="A15" s="18">
         <v>46255</v>
       </c>
       <c r="B15" s="10">
@@ -1336,7 +1338,7 @@
       </c>
     </row>
     <row r="16" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A16" s="23">
+      <c r="A16" s="18">
         <v>46256</v>
       </c>
       <c r="B16" s="10">
@@ -1380,7 +1382,7 @@
       </c>
     </row>
     <row r="17" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A17" s="23">
+      <c r="A17" s="18">
         <v>46257</v>
       </c>
       <c r="B17" s="10">
@@ -1425,7 +1427,7 @@
       <c r="O17" s="10"/>
     </row>
     <row r="18" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A18" s="24">
+      <c r="A18" s="19">
         <v>46258</v>
       </c>
       <c r="B18" s="10">
@@ -1469,7 +1471,7 @@
       </c>
     </row>
     <row r="19" spans="1:15" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A19" s="23">
+      <c r="A19" s="18">
         <v>46259</v>
       </c>
       <c r="B19" s="10">
@@ -1513,7 +1515,7 @@
       </c>
     </row>
     <row r="20" spans="1:15" ht="13.2" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A20" s="23">
+      <c r="A20" s="18">
         <v>46260</v>
       </c>
       <c r="B20" s="12">
@@ -1557,7 +1559,7 @@
       </c>
     </row>
     <row r="21" spans="1:15" ht="13.8" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A21" s="23">
+      <c r="A21" s="18">
         <v>46261</v>
       </c>
       <c r="B21" s="14">
@@ -1601,7 +1603,7 @@
       </c>
     </row>
     <row r="22" spans="1:15" ht="13.2" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A22" s="25">
+      <c r="A22" s="20">
         <v>46262</v>
       </c>
       <c r="B22" s="15">
@@ -1616,7 +1618,7 @@
       <c r="E22" s="13">
         <v>180</v>
       </c>
-      <c r="F22" s="16">
+      <c r="F22" s="13">
         <v>0</v>
       </c>
       <c r="G22" s="13">
@@ -1645,7 +1647,7 @@
       </c>
     </row>
     <row r="23" spans="1:15" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A23" s="25">
+      <c r="A23" s="20">
         <v>46263</v>
       </c>
       <c r="B23" s="15">
@@ -1660,7 +1662,7 @@
       <c r="E23" s="13">
         <v>240</v>
       </c>
-      <c r="F23" s="16">
+      <c r="F23" s="13">
         <v>0</v>
       </c>
       <c r="G23" s="13">
@@ -1689,7 +1691,7 @@
       </c>
     </row>
     <row r="24" spans="1:15" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A24" s="25">
+      <c r="A24" s="20">
         <v>46264</v>
       </c>
       <c r="B24" s="15">
@@ -1704,7 +1706,7 @@
       <c r="E24" s="13">
         <v>180</v>
       </c>
-      <c r="F24" s="16">
+      <c r="F24" s="13">
         <v>0</v>
       </c>
       <c r="G24" s="13">
@@ -1733,7 +1735,7 @@
       </c>
     </row>
     <row r="25" spans="1:15" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A25" s="25">
+      <c r="A25" s="20">
         <v>46265</v>
       </c>
       <c r="B25" s="15">
@@ -1748,7 +1750,7 @@
       <c r="E25" s="13">
         <v>150</v>
       </c>
-      <c r="F25" s="22">
+      <c r="F25" s="17">
         <v>100</v>
       </c>
       <c r="G25" s="13">
@@ -1777,7 +1779,7 @@
       </c>
     </row>
     <row r="26" spans="1:15" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A26" s="25">
+      <c r="A26" s="20">
         <v>46266</v>
       </c>
       <c r="B26" s="15">
@@ -1792,7 +1794,7 @@
       <c r="E26" s="13">
         <v>120</v>
       </c>
-      <c r="F26" s="22">
+      <c r="F26" s="17">
         <v>350</v>
       </c>
       <c r="G26" s="13">
@@ -1821,34 +1823,34 @@
       </c>
     </row>
     <row r="27" spans="1:15" ht="15.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A27" s="21">
+      <c r="A27" s="16">
         <v>46267</v>
       </c>
-      <c r="B27" s="22">
+      <c r="B27" s="17">
         <v>360</v>
       </c>
-      <c r="C27" s="22">
+      <c r="C27" s="17">
         <v>45</v>
       </c>
-      <c r="D27" s="22">
+      <c r="D27" s="17">
         <v>150</v>
       </c>
-      <c r="E27" s="22">
+      <c r="E27" s="17">
         <v>150</v>
       </c>
-      <c r="F27" s="22">
+      <c r="F27" s="17">
         <v>200</v>
       </c>
-      <c r="G27" s="22">
+      <c r="G27" s="17">
         <v>4</v>
       </c>
-      <c r="H27" s="22">
+      <c r="H27" s="17">
         <v>240</v>
       </c>
-      <c r="I27" s="22">
+      <c r="I27" s="17">
         <v>1145</v>
       </c>
-      <c r="J27" s="22">
+      <c r="J27" s="17">
         <v>295</v>
       </c>
       <c r="K27" s="13" t="s">
@@ -1857,7 +1859,7 @@
       <c r="L27" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="M27" s="28" t="s">
+      <c r="M27" s="22" t="s">
         <v>26</v>
       </c>
       <c r="N27" s="13" t="s">
@@ -1865,34 +1867,34 @@
       </c>
     </row>
     <row r="28" spans="1:15" ht="17.399999999999999" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A28" s="21">
+      <c r="A28" s="16">
         <v>46268</v>
       </c>
-      <c r="B28" s="22">
+      <c r="B28" s="17">
         <v>360</v>
       </c>
-      <c r="C28" s="22">
+      <c r="C28" s="17">
         <v>30</v>
       </c>
-      <c r="D28" s="22">
+      <c r="D28" s="17">
         <v>120</v>
       </c>
-      <c r="E28" s="22">
+      <c r="E28" s="17">
         <v>120</v>
       </c>
-      <c r="F28" s="22">
+      <c r="F28" s="17">
         <v>350</v>
       </c>
-      <c r="G28" s="22">
+      <c r="G28" s="17">
         <v>7</v>
       </c>
-      <c r="H28" s="22">
+      <c r="H28" s="17">
         <v>360</v>
       </c>
-      <c r="I28" s="22">
+      <c r="I28" s="17">
         <v>1340</v>
       </c>
-      <c r="J28" s="22">
+      <c r="J28" s="17">
         <v>100</v>
       </c>
       <c r="K28" s="13" t="s">
@@ -1901,7 +1903,7 @@
       <c r="L28" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="M28" s="28" t="s">
+      <c r="M28" s="22" t="s">
         <v>29</v>
       </c>
       <c r="N28" s="13" t="s">
@@ -1909,34 +1911,34 @@
       </c>
     </row>
     <row r="29" spans="1:15" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A29" s="21">
+      <c r="A29" s="16">
         <v>46269</v>
       </c>
-      <c r="B29" s="22">
+      <c r="B29" s="17">
         <v>360</v>
       </c>
-      <c r="C29" s="22">
+      <c r="C29" s="17">
         <v>30</v>
       </c>
-      <c r="D29" s="22">
+      <c r="D29" s="17">
         <v>120</v>
       </c>
-      <c r="E29" s="22">
+      <c r="E29" s="17">
         <v>120</v>
       </c>
-      <c r="F29" s="22">
+      <c r="F29" s="17">
         <v>350</v>
       </c>
-      <c r="G29" s="22">
+      <c r="G29" s="17">
         <v>7</v>
       </c>
-      <c r="H29" s="22">
+      <c r="H29" s="17">
         <v>360</v>
       </c>
-      <c r="I29" s="22">
+      <c r="I29" s="17">
         <v>1340</v>
       </c>
-      <c r="J29" s="26">
+      <c r="J29">
         <v>100</v>
       </c>
       <c r="K29" s="13" t="s">
@@ -1945,7 +1947,7 @@
       <c r="L29" s="13" t="s">
         <v>29</v>
       </c>
-      <c r="M29" s="28" t="s">
+      <c r="M29" s="22" t="s">
         <v>29</v>
       </c>
       <c r="N29" s="13" t="s">
@@ -1953,34 +1955,34 @@
       </c>
     </row>
     <row r="30" spans="1:15" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A30" s="21">
+      <c r="A30" s="16">
         <v>46270</v>
       </c>
-      <c r="B30" s="22">
+      <c r="B30" s="17">
         <v>450</v>
       </c>
-      <c r="C30" s="22">
+      <c r="C30" s="17">
         <v>60</v>
       </c>
-      <c r="D30" s="22">
+      <c r="D30" s="17">
         <v>240</v>
       </c>
-      <c r="E30" s="22">
+      <c r="E30" s="17">
         <v>210</v>
       </c>
-      <c r="F30" s="22">
+      <c r="F30" s="17">
         <v>0</v>
       </c>
-      <c r="G30" s="22">
+      <c r="G30" s="17">
         <v>0</v>
       </c>
-      <c r="H30" s="22">
+      <c r="H30" s="17">
         <v>240</v>
       </c>
-      <c r="I30" s="22">
+      <c r="I30" s="17">
         <v>1200</v>
       </c>
-      <c r="J30" s="22">
+      <c r="J30" s="17">
         <v>240</v>
       </c>
       <c r="K30" s="13" t="s">
@@ -1989,56 +1991,100 @@
       <c r="L30" s="13" t="s">
         <v>30</v>
       </c>
-      <c r="M30" s="28" t="s">
+      <c r="M30" s="22" t="s">
         <v>26</v>
       </c>
       <c r="N30" s="13" t="s">
         <v>51</v>
       </c>
     </row>
-    <row r="31" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A31" s="5"/>
-      <c r="B31" s="6"/>
-      <c r="C31" s="6"/>
-      <c r="D31" s="6"/>
-      <c r="E31" s="6"/>
-      <c r="F31" s="6"/>
-      <c r="G31" s="6"/>
-      <c r="H31" s="6"/>
-      <c r="I31" s="4" t="str">
-        <f t="shared" ref="I31:I41" si="0">IF(SUM(B31:F31,H31)=0,"",SUM(B31:F31,H31))</f>
-        <v/>
-      </c>
-      <c r="J31" s="4" t="str">
-        <f t="shared" ref="J31:J41" si="1">IF(I31="","",1440-I31)</f>
-        <v/>
-      </c>
-      <c r="K31" s="7"/>
-      <c r="L31" s="7"/>
-      <c r="M31" s="7"/>
-      <c r="N31" s="17"/>
-    </row>
-    <row r="32" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A32" s="5"/>
-      <c r="B32" s="6"/>
-      <c r="C32" s="6"/>
-      <c r="D32" s="6"/>
-      <c r="E32" s="6"/>
-      <c r="F32" s="6"/>
-      <c r="G32" s="6"/>
-      <c r="H32" s="6"/>
-      <c r="I32" s="4" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J32" s="4" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K32" s="7"/>
-      <c r="L32" s="7"/>
-      <c r="M32" s="7"/>
-      <c r="N32" s="8"/>
+    <row r="31" spans="1:15" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A31" s="26">
+        <v>46271</v>
+      </c>
+      <c r="B31" s="13">
+        <v>450</v>
+      </c>
+      <c r="C31" s="13">
+        <v>45</v>
+      </c>
+      <c r="D31" s="13">
+        <v>300</v>
+      </c>
+      <c r="E31" s="13">
+        <v>150</v>
+      </c>
+      <c r="F31" s="13">
+        <v>0</v>
+      </c>
+      <c r="G31" s="13">
+        <v>0</v>
+      </c>
+      <c r="H31" s="13">
+        <v>210</v>
+      </c>
+      <c r="I31" s="13">
+        <v>1155</v>
+      </c>
+      <c r="J31" s="13">
+        <v>285</v>
+      </c>
+      <c r="K31" s="13" t="s">
+        <v>32</v>
+      </c>
+      <c r="L31" s="13" t="s">
+        <v>30</v>
+      </c>
+      <c r="M31" s="13" t="s">
+        <v>26</v>
+      </c>
+      <c r="N31" s="13" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="32" spans="1:15" ht="19.2" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A32" s="26">
+        <v>46272</v>
+      </c>
+      <c r="B32" s="13">
+        <v>330</v>
+      </c>
+      <c r="C32" s="13">
+        <v>30</v>
+      </c>
+      <c r="D32" s="13">
+        <v>240</v>
+      </c>
+      <c r="E32" s="13">
+        <v>120</v>
+      </c>
+      <c r="F32" s="13">
+        <v>150</v>
+      </c>
+      <c r="G32" s="13">
+        <v>3</v>
+      </c>
+      <c r="H32" s="13">
+        <v>330</v>
+      </c>
+      <c r="I32" s="13">
+        <v>1200</v>
+      </c>
+      <c r="J32" s="13">
+        <v>240</v>
+      </c>
+      <c r="K32" s="13" t="s">
+        <v>42</v>
+      </c>
+      <c r="L32" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="M32" s="13" t="s">
+        <v>29</v>
+      </c>
+      <c r="N32" s="13" t="s">
+        <v>65</v>
+      </c>
     </row>
     <row r="33" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A33" s="5"/>
@@ -2050,11 +2096,11 @@
       <c r="G33" s="6"/>
       <c r="H33" s="6"/>
       <c r="I33" s="4" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" ref="I33:I40" si="0">IF(SUM(B33:F33,H33)=0,"",SUM(B33:F33,H33))</f>
         <v/>
       </c>
       <c r="J33" s="4" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" ref="J33:J40" si="1">IF(I33="","",1440-I33)</f>
         <v/>
       </c>
       <c r="K33" s="7"/>
@@ -2226,11 +2272,11 @@
       <c r="G41" s="6"/>
       <c r="H41" s="6"/>
       <c r="I41" s="4" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" ref="I41:I104" si="2">IF(SUM(B41:F41,H41)=0,"",SUM(B41:F41,H41))</f>
         <v/>
       </c>
       <c r="J41" s="4" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" ref="J41:J104" si="3">IF(I41="","",1440-I41)</f>
         <v/>
       </c>
       <c r="K41" s="7"/>
@@ -2248,11 +2294,11 @@
       <c r="G42" s="6"/>
       <c r="H42" s="6"/>
       <c r="I42" s="4" t="str">
-        <f t="shared" ref="I42:I105" si="2">IF(SUM(B42:F42,H42)=0,"",SUM(B42:F42,H42))</f>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="J42" s="4" t="str">
-        <f t="shared" ref="J42:J105" si="3">IF(I42="","",1440-I42)</f>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="K42" s="7"/>
@@ -3634,11 +3680,11 @@
       <c r="G105" s="6"/>
       <c r="H105" s="6"/>
       <c r="I105" s="4" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" ref="I105:I168" si="4">IF(SUM(B105:F105,H105)=0,"",SUM(B105:F105,H105))</f>
         <v/>
       </c>
       <c r="J105" s="4" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" ref="J105:J168" si="5">IF(I105="","",1440-I105)</f>
         <v/>
       </c>
       <c r="K105" s="7"/>
@@ -3656,11 +3702,11 @@
       <c r="G106" s="6"/>
       <c r="H106" s="6"/>
       <c r="I106" s="4" t="str">
-        <f t="shared" ref="I106:I169" si="4">IF(SUM(B106:F106,H106)=0,"",SUM(B106:F106,H106))</f>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J106" s="4" t="str">
-        <f t="shared" ref="J106:J169" si="5">IF(I106="","",1440-I106)</f>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K106" s="7"/>
@@ -5042,11 +5088,11 @@
       <c r="G169" s="6"/>
       <c r="H169" s="6"/>
       <c r="I169" s="4" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" ref="I169:I232" si="6">IF(SUM(B169:F169,H169)=0,"",SUM(B169:F169,H169))</f>
         <v/>
       </c>
       <c r="J169" s="4" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" ref="J169:J232" si="7">IF(I169="","",1440-I169)</f>
         <v/>
       </c>
       <c r="K169" s="7"/>
@@ -5064,11 +5110,11 @@
       <c r="G170" s="6"/>
       <c r="H170" s="6"/>
       <c r="I170" s="4" t="str">
-        <f t="shared" ref="I170:I233" si="6">IF(SUM(B170:F170,H170)=0,"",SUM(B170:F170,H170))</f>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J170" s="4" t="str">
-        <f t="shared" ref="J170:J233" si="7">IF(I170="","",1440-I170)</f>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K170" s="7"/>
@@ -6450,11 +6496,11 @@
       <c r="G233" s="6"/>
       <c r="H233" s="6"/>
       <c r="I233" s="4" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" ref="I233:I296" si="8">IF(SUM(B233:F233,H233)=0,"",SUM(B233:F233,H233))</f>
         <v/>
       </c>
       <c r="J233" s="4" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" ref="J233:J296" si="9">IF(I233="","",1440-I233)</f>
         <v/>
       </c>
       <c r="K233" s="7"/>
@@ -6472,11 +6518,11 @@
       <c r="G234" s="6"/>
       <c r="H234" s="6"/>
       <c r="I234" s="4" t="str">
-        <f t="shared" ref="I234:I297" si="8">IF(SUM(B234:F234,H234)=0,"",SUM(B234:F234,H234))</f>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J234" s="4" t="str">
-        <f t="shared" ref="J234:J297" si="9">IF(I234="","",1440-I234)</f>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K234" s="7"/>
@@ -7858,11 +7904,11 @@
       <c r="G297" s="6"/>
       <c r="H297" s="6"/>
       <c r="I297" s="4" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" ref="I297:I360" si="10">IF(SUM(B297:F297,H297)=0,"",SUM(B297:F297,H297))</f>
         <v/>
       </c>
       <c r="J297" s="4" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" ref="J297:J360" si="11">IF(I297="","",1440-I297)</f>
         <v/>
       </c>
       <c r="K297" s="7"/>
@@ -7880,11 +7926,11 @@
       <c r="G298" s="6"/>
       <c r="H298" s="6"/>
       <c r="I298" s="4" t="str">
-        <f t="shared" ref="I298:I361" si="10">IF(SUM(B298:F298,H298)=0,"",SUM(B298:F298,H298))</f>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J298" s="4" t="str">
-        <f t="shared" ref="J298:J361" si="11">IF(I298="","",1440-I298)</f>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K298" s="7"/>
@@ -9266,11 +9312,11 @@
       <c r="G361" s="6"/>
       <c r="H361" s="6"/>
       <c r="I361" s="4" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" ref="I361:I373" si="12">IF(SUM(B361:F361,H361)=0,"",SUM(B361:F361,H361))</f>
         <v/>
       </c>
       <c r="J361" s="4" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" ref="J361:J373" si="13">IF(I361="","",1440-I361)</f>
         <v/>
       </c>
       <c r="K361" s="7"/>
@@ -9288,11 +9334,11 @@
       <c r="G362" s="6"/>
       <c r="H362" s="6"/>
       <c r="I362" s="4" t="str">
-        <f t="shared" ref="I362:I374" si="12">IF(SUM(B362:F362,H362)=0,"",SUM(B362:F362,H362))</f>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J362" s="4" t="str">
-        <f t="shared" ref="J362:J374" si="13">IF(I362="","",1440-I362)</f>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K362" s="7"/>
@@ -9499,14 +9545,6 @@
       <c r="N371" s="8"/>
     </row>
     <row r="372" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A372" s="5"/>
-      <c r="B372" s="6"/>
-      <c r="C372" s="6"/>
-      <c r="D372" s="6"/>
-      <c r="E372" s="6"/>
-      <c r="F372" s="6"/>
-      <c r="G372" s="6"/>
-      <c r="H372" s="6"/>
       <c r="I372" s="4" t="str">
         <f t="shared" si="12"/>
         <v/>
@@ -9515,10 +9553,6 @@
         <f t="shared" si="13"/>
         <v/>
       </c>
-      <c r="K372" s="7"/>
-      <c r="L372" s="7"/>
-      <c r="M372" s="7"/>
-      <c r="N372" s="8"/>
     </row>
     <row r="373" spans="1:14" x14ac:dyDescent="0.3">
       <c r="I373" s="4" t="str">
@@ -9526,16 +9560,6 @@
         <v/>
       </c>
       <c r="J373" s="4" t="str">
-        <f t="shared" si="13"/>
-        <v/>
-      </c>
-    </row>
-    <row r="374" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="I374" s="4" t="str">
-        <f t="shared" si="12"/>
-        <v/>
-      </c>
-      <c r="J374" s="4" t="str">
         <f t="shared" si="13"/>
         <v/>
       </c>

--- a/CAP776 (PYTHON).xlsx
+++ b/CAP776 (PYTHON).xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\palak\Downloads\776(clone)\776\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2A5F7AD6-29CD-4941-AEAB-420C3F1BD014}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F87CBFFE-6098-49E3-89BB-70DF1752347E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{327CE7B2-1886-45B8-951C-28CB36CE6AAF}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="131" uniqueCount="66">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="147" uniqueCount="71">
   <si>
     <t>My Data, My Code — Daily Log</t>
   </si>
@@ -233,6 +233,21 @@
   <si>
     <t>Woke up early at 4 AM for CA prep, attended 3 classes &amp; rested after home</t>
   </si>
+  <si>
+    <t>Full schedule with 7 classes and routine travel</t>
+  </si>
+  <si>
+    <t>Attended 4 classes &amp; spent extra time on coding practice</t>
+  </si>
+  <si>
+    <t>Excited</t>
+  </si>
+  <si>
+    <t>Attended 7 classes, freshers party event, &amp; late evening CA prep</t>
+  </si>
+  <si>
+    <t>Attended 7 lectures &amp; revised all previous topics</t>
+  </si>
 </sst>
 </file>
 
@@ -410,17 +425,7 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="14" fontId="7" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="14" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="3" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -432,7 +437,17 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="1" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="14" fontId="7" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -750,7 +765,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6E7F1806-3D91-4029-8849-359DB02F0997}">
-  <dimension ref="A1:O373"/>
+  <dimension ref="A1:O372"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="15.21875" customWidth="1"/>
@@ -770,39 +785,39 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:14" ht="16.8" x14ac:dyDescent="0.3">
-      <c r="A1" s="24" t="s">
+      <c r="A1" s="20" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="24"/>
-      <c r="C1" s="24"/>
-      <c r="D1" s="24"/>
-      <c r="E1" s="24"/>
-      <c r="F1" s="24"/>
-      <c r="G1" s="24"/>
-      <c r="H1" s="24"/>
-      <c r="I1" s="24"/>
-      <c r="J1" s="24"/>
-      <c r="K1" s="24"/>
-      <c r="L1" s="24"/>
-      <c r="M1" s="24"/>
-      <c r="N1" s="24"/>
+      <c r="B1" s="20"/>
+      <c r="C1" s="20"/>
+      <c r="D1" s="20"/>
+      <c r="E1" s="20"/>
+      <c r="F1" s="20"/>
+      <c r="G1" s="20"/>
+      <c r="H1" s="20"/>
+      <c r="I1" s="20"/>
+      <c r="J1" s="20"/>
+      <c r="K1" s="20"/>
+      <c r="L1" s="20"/>
+      <c r="M1" s="20"/>
+      <c r="N1" s="20"/>
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A2" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="25" t="s">
+      <c r="B2" s="21" t="s">
         <v>23</v>
       </c>
-      <c r="C2" s="25"/>
-      <c r="D2" s="25"/>
+      <c r="C2" s="21"/>
+      <c r="D2" s="21"/>
       <c r="E2" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="F2" s="25">
+      <c r="F2" s="21">
         <v>12617802</v>
       </c>
-      <c r="G2" s="25"/>
+      <c r="G2" s="21"/>
       <c r="H2" s="1"/>
       <c r="I2" s="1"/>
       <c r="J2" s="1"/>
@@ -815,18 +830,18 @@
       <c r="A3" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="B3" s="25" t="s">
+      <c r="B3" s="21" t="s">
         <v>21</v>
       </c>
-      <c r="C3" s="25"/>
-      <c r="D3" s="25"/>
+      <c r="C3" s="21"/>
+      <c r="D3" s="21"/>
       <c r="E3" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="F3" s="25" t="s">
+      <c r="F3" s="21" t="s">
         <v>22</v>
       </c>
-      <c r="G3" s="25"/>
+      <c r="G3" s="21"/>
       <c r="H3" s="1"/>
       <c r="I3" s="1"/>
       <c r="J3" s="1"/>
@@ -836,22 +851,22 @@
       <c r="N3" s="1"/>
     </row>
     <row r="4" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A4" s="23" t="s">
+      <c r="A4" s="19" t="s">
         <v>5</v>
       </c>
-      <c r="B4" s="23"/>
-      <c r="C4" s="23"/>
-      <c r="D4" s="23"/>
-      <c r="E4" s="23"/>
-      <c r="F4" s="23"/>
-      <c r="G4" s="23"/>
-      <c r="H4" s="23"/>
-      <c r="I4" s="23"/>
-      <c r="J4" s="23"/>
-      <c r="K4" s="23"/>
-      <c r="L4" s="23"/>
-      <c r="M4" s="23"/>
-      <c r="N4" s="23"/>
+      <c r="B4" s="19"/>
+      <c r="C4" s="19"/>
+      <c r="D4" s="19"/>
+      <c r="E4" s="19"/>
+      <c r="F4" s="19"/>
+      <c r="G4" s="19"/>
+      <c r="H4" s="19"/>
+      <c r="I4" s="19"/>
+      <c r="J4" s="19"/>
+      <c r="K4" s="19"/>
+      <c r="L4" s="19"/>
+      <c r="M4" s="19"/>
+      <c r="N4" s="19"/>
     </row>
     <row r="5" spans="1:14" ht="52.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="3" t="s">
@@ -893,12 +908,12 @@
       <c r="M5" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="N5" s="21" t="s">
+      <c r="N5" s="17" t="s">
         <v>19</v>
       </c>
     </row>
     <row r="6" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A6" s="18">
+      <c r="A6" s="23">
         <v>46246</v>
       </c>
       <c r="B6" s="9">
@@ -942,7 +957,7 @@
       </c>
     </row>
     <row r="7" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A7" s="18">
+      <c r="A7" s="23">
         <v>46247</v>
       </c>
       <c r="B7" s="9">
@@ -986,7 +1001,7 @@
       </c>
     </row>
     <row r="8" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A8" s="18">
+      <c r="A8" s="23">
         <v>46248</v>
       </c>
       <c r="B8" s="9">
@@ -1030,7 +1045,7 @@
       </c>
     </row>
     <row r="9" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A9" s="18">
+      <c r="A9" s="23">
         <v>46249</v>
       </c>
       <c r="B9" s="9">
@@ -1074,7 +1089,7 @@
       </c>
     </row>
     <row r="10" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A10" s="18">
+      <c r="A10" s="23">
         <v>46250</v>
       </c>
       <c r="B10" s="9">
@@ -1118,7 +1133,7 @@
       </c>
     </row>
     <row r="11" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A11" s="18">
+      <c r="A11" s="23">
         <v>46251</v>
       </c>
       <c r="B11" s="10">
@@ -1162,7 +1177,7 @@
       </c>
     </row>
     <row r="12" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A12" s="18">
+      <c r="A12" s="23">
         <v>46252</v>
       </c>
       <c r="B12" s="10">
@@ -1206,7 +1221,7 @@
       </c>
     </row>
     <row r="13" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A13" s="18">
+      <c r="A13" s="23">
         <v>46253</v>
       </c>
       <c r="B13" s="10">
@@ -1250,7 +1265,7 @@
       </c>
     </row>
     <row r="14" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A14" s="18">
+      <c r="A14" s="23">
         <v>46254</v>
       </c>
       <c r="B14" s="10">
@@ -1294,7 +1309,7 @@
       </c>
     </row>
     <row r="15" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A15" s="18">
+      <c r="A15" s="23">
         <v>46255</v>
       </c>
       <c r="B15" s="10">
@@ -1338,7 +1353,7 @@
       </c>
     </row>
     <row r="16" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A16" s="18">
+      <c r="A16" s="23">
         <v>46256</v>
       </c>
       <c r="B16" s="10">
@@ -1382,7 +1397,7 @@
       </c>
     </row>
     <row r="17" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A17" s="18">
+      <c r="A17" s="23">
         <v>46257</v>
       </c>
       <c r="B17" s="10">
@@ -1427,7 +1442,7 @@
       <c r="O17" s="10"/>
     </row>
     <row r="18" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A18" s="19">
+      <c r="A18" s="24">
         <v>46258</v>
       </c>
       <c r="B18" s="10">
@@ -1471,7 +1486,7 @@
       </c>
     </row>
     <row r="19" spans="1:15" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A19" s="18">
+      <c r="A19" s="23">
         <v>46259</v>
       </c>
       <c r="B19" s="10">
@@ -1515,7 +1530,7 @@
       </c>
     </row>
     <row r="20" spans="1:15" ht="13.2" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A20" s="18">
+      <c r="A20" s="23">
         <v>46260</v>
       </c>
       <c r="B20" s="12">
@@ -1559,7 +1574,7 @@
       </c>
     </row>
     <row r="21" spans="1:15" ht="13.8" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A21" s="18">
+      <c r="A21" s="23">
         <v>46261</v>
       </c>
       <c r="B21" s="14">
@@ -1603,7 +1618,7 @@
       </c>
     </row>
     <row r="22" spans="1:15" ht="13.2" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A22" s="20">
+      <c r="A22" s="25">
         <v>46262</v>
       </c>
       <c r="B22" s="15">
@@ -1647,7 +1662,7 @@
       </c>
     </row>
     <row r="23" spans="1:15" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A23" s="20">
+      <c r="A23" s="25">
         <v>46263</v>
       </c>
       <c r="B23" s="15">
@@ -1691,7 +1706,7 @@
       </c>
     </row>
     <row r="24" spans="1:15" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A24" s="20">
+      <c r="A24" s="25">
         <v>46264</v>
       </c>
       <c r="B24" s="15">
@@ -1735,7 +1750,7 @@
       </c>
     </row>
     <row r="25" spans="1:15" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A25" s="20">
+      <c r="A25" s="25">
         <v>46265</v>
       </c>
       <c r="B25" s="15">
@@ -1750,7 +1765,7 @@
       <c r="E25" s="13">
         <v>150</v>
       </c>
-      <c r="F25" s="17">
+      <c r="F25" s="16">
         <v>100</v>
       </c>
       <c r="G25" s="13">
@@ -1779,7 +1794,7 @@
       </c>
     </row>
     <row r="26" spans="1:15" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A26" s="20">
+      <c r="A26" s="25">
         <v>46266</v>
       </c>
       <c r="B26" s="15">
@@ -1794,7 +1809,7 @@
       <c r="E26" s="13">
         <v>120</v>
       </c>
-      <c r="F26" s="17">
+      <c r="F26" s="16">
         <v>350</v>
       </c>
       <c r="G26" s="13">
@@ -1823,34 +1838,34 @@
       </c>
     </row>
     <row r="27" spans="1:15" ht="15.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A27" s="16">
+      <c r="A27" s="25">
         <v>46267</v>
       </c>
-      <c r="B27" s="17">
+      <c r="B27" s="16">
         <v>360</v>
       </c>
-      <c r="C27" s="17">
+      <c r="C27" s="16">
         <v>45</v>
       </c>
-      <c r="D27" s="17">
+      <c r="D27" s="16">
         <v>150</v>
       </c>
-      <c r="E27" s="17">
+      <c r="E27" s="16">
         <v>150</v>
       </c>
-      <c r="F27" s="17">
+      <c r="F27" s="16">
         <v>200</v>
       </c>
-      <c r="G27" s="17">
+      <c r="G27" s="16">
         <v>4</v>
       </c>
-      <c r="H27" s="17">
+      <c r="H27" s="16">
         <v>240</v>
       </c>
-      <c r="I27" s="17">
+      <c r="I27" s="16">
         <v>1145</v>
       </c>
-      <c r="J27" s="17">
+      <c r="J27" s="16">
         <v>295</v>
       </c>
       <c r="K27" s="13" t="s">
@@ -1859,7 +1874,7 @@
       <c r="L27" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="M27" s="22" t="s">
+      <c r="M27" s="18" t="s">
         <v>26</v>
       </c>
       <c r="N27" s="13" t="s">
@@ -1867,34 +1882,34 @@
       </c>
     </row>
     <row r="28" spans="1:15" ht="17.399999999999999" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A28" s="16">
+      <c r="A28" s="25">
         <v>46268</v>
       </c>
-      <c r="B28" s="17">
+      <c r="B28" s="16">
         <v>360</v>
       </c>
-      <c r="C28" s="17">
+      <c r="C28" s="16">
         <v>30</v>
       </c>
-      <c r="D28" s="17">
+      <c r="D28" s="16">
         <v>120</v>
       </c>
-      <c r="E28" s="17">
+      <c r="E28" s="16">
         <v>120</v>
       </c>
-      <c r="F28" s="17">
+      <c r="F28" s="16">
         <v>350</v>
       </c>
-      <c r="G28" s="17">
+      <c r="G28" s="16">
         <v>7</v>
       </c>
-      <c r="H28" s="17">
+      <c r="H28" s="16">
         <v>360</v>
       </c>
-      <c r="I28" s="17">
+      <c r="I28" s="16">
         <v>1340</v>
       </c>
-      <c r="J28" s="17">
+      <c r="J28" s="16">
         <v>100</v>
       </c>
       <c r="K28" s="13" t="s">
@@ -1903,7 +1918,7 @@
       <c r="L28" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="M28" s="22" t="s">
+      <c r="M28" s="18" t="s">
         <v>29</v>
       </c>
       <c r="N28" s="13" t="s">
@@ -1911,31 +1926,31 @@
       </c>
     </row>
     <row r="29" spans="1:15" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A29" s="16">
+      <c r="A29" s="25">
         <v>46269</v>
       </c>
-      <c r="B29" s="17">
+      <c r="B29" s="16">
         <v>360</v>
       </c>
-      <c r="C29" s="17">
+      <c r="C29" s="16">
         <v>30</v>
       </c>
-      <c r="D29" s="17">
+      <c r="D29" s="16">
         <v>120</v>
       </c>
-      <c r="E29" s="17">
+      <c r="E29" s="16">
         <v>120</v>
       </c>
-      <c r="F29" s="17">
+      <c r="F29" s="16">
         <v>350</v>
       </c>
-      <c r="G29" s="17">
+      <c r="G29" s="16">
         <v>7</v>
       </c>
-      <c r="H29" s="17">
+      <c r="H29" s="16">
         <v>360</v>
       </c>
-      <c r="I29" s="17">
+      <c r="I29" s="16">
         <v>1340</v>
       </c>
       <c r="J29">
@@ -1947,7 +1962,7 @@
       <c r="L29" s="13" t="s">
         <v>29</v>
       </c>
-      <c r="M29" s="22" t="s">
+      <c r="M29" s="18" t="s">
         <v>29</v>
       </c>
       <c r="N29" s="13" t="s">
@@ -1955,34 +1970,34 @@
       </c>
     </row>
     <row r="30" spans="1:15" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A30" s="16">
+      <c r="A30" s="25">
         <v>46270</v>
       </c>
-      <c r="B30" s="17">
+      <c r="B30" s="16">
         <v>450</v>
       </c>
-      <c r="C30" s="17">
+      <c r="C30" s="16">
         <v>60</v>
       </c>
-      <c r="D30" s="17">
+      <c r="D30" s="16">
         <v>240</v>
       </c>
-      <c r="E30" s="17">
+      <c r="E30" s="16">
         <v>210</v>
       </c>
-      <c r="F30" s="17">
+      <c r="F30" s="16">
         <v>0</v>
       </c>
-      <c r="G30" s="17">
+      <c r="G30" s="16">
         <v>0</v>
       </c>
-      <c r="H30" s="17">
+      <c r="H30" s="16">
         <v>240</v>
       </c>
-      <c r="I30" s="17">
+      <c r="I30" s="16">
         <v>1200</v>
       </c>
-      <c r="J30" s="17">
+      <c r="J30" s="16">
         <v>240</v>
       </c>
       <c r="K30" s="13" t="s">
@@ -1991,7 +2006,7 @@
       <c r="L30" s="13" t="s">
         <v>30</v>
       </c>
-      <c r="M30" s="22" t="s">
+      <c r="M30" s="18" t="s">
         <v>26</v>
       </c>
       <c r="N30" s="13" t="s">
@@ -2086,93 +2101,181 @@
         <v>65</v>
       </c>
     </row>
-    <row r="33" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A33" s="5"/>
-      <c r="B33" s="6"/>
-      <c r="C33" s="6"/>
-      <c r="D33" s="6"/>
-      <c r="E33" s="6"/>
-      <c r="F33" s="6"/>
-      <c r="G33" s="6"/>
-      <c r="H33" s="6"/>
-      <c r="I33" s="4" t="str">
-        <f t="shared" ref="I33:I40" si="0">IF(SUM(B33:F33,H33)=0,"",SUM(B33:F33,H33))</f>
-        <v/>
-      </c>
-      <c r="J33" s="4" t="str">
-        <f t="shared" ref="J33:J40" si="1">IF(I33="","",1440-I33)</f>
-        <v/>
-      </c>
-      <c r="K33" s="7"/>
-      <c r="L33" s="7"/>
-      <c r="M33" s="7"/>
-      <c r="N33" s="8"/>
-    </row>
-    <row r="34" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A34" s="5"/>
-      <c r="B34" s="6"/>
-      <c r="C34" s="6"/>
-      <c r="D34" s="6"/>
-      <c r="E34" s="6"/>
-      <c r="F34" s="6"/>
-      <c r="G34" s="6"/>
-      <c r="H34" s="6"/>
-      <c r="I34" s="4" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J34" s="4" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K34" s="7"/>
-      <c r="L34" s="7"/>
-      <c r="M34" s="7"/>
-      <c r="N34" s="8"/>
-    </row>
-    <row r="35" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A35" s="5"/>
-      <c r="B35" s="6"/>
-      <c r="C35" s="6"/>
-      <c r="D35" s="6"/>
-      <c r="E35" s="6"/>
-      <c r="F35" s="6"/>
-      <c r="G35" s="6"/>
-      <c r="H35" s="6"/>
-      <c r="I35" s="4" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J35" s="4" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K35" s="7"/>
-      <c r="L35" s="7"/>
-      <c r="M35" s="7"/>
-      <c r="N35" s="8"/>
-    </row>
-    <row r="36" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A36" s="5"/>
-      <c r="B36" s="6"/>
-      <c r="C36" s="6"/>
-      <c r="D36" s="6"/>
-      <c r="E36" s="6"/>
-      <c r="F36" s="6"/>
-      <c r="G36" s="6"/>
-      <c r="H36" s="6"/>
-      <c r="I36" s="4" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J36" s="4" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K36" s="7"/>
-      <c r="L36" s="7"/>
-      <c r="M36" s="7"/>
-      <c r="N36" s="8"/>
+    <row r="33" spans="1:14" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A33" s="26">
+        <v>46273</v>
+      </c>
+      <c r="B33" s="13">
+        <v>360</v>
+      </c>
+      <c r="C33" s="13">
+        <v>30</v>
+      </c>
+      <c r="D33" s="13">
+        <v>120</v>
+      </c>
+      <c r="E33" s="13">
+        <v>120</v>
+      </c>
+      <c r="F33" s="13">
+        <v>350</v>
+      </c>
+      <c r="G33" s="13">
+        <v>7</v>
+      </c>
+      <c r="H33" s="13">
+        <v>360</v>
+      </c>
+      <c r="I33" s="13">
+        <v>1340</v>
+      </c>
+      <c r="J33" s="13">
+        <v>100</v>
+      </c>
+      <c r="K33" s="13" t="s">
+        <v>34</v>
+      </c>
+      <c r="L33" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="M33" s="13" t="s">
+        <v>29</v>
+      </c>
+      <c r="N33" s="22" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="34" spans="1:14" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A34" s="26">
+        <v>46274</v>
+      </c>
+      <c r="B34" s="13">
+        <v>360</v>
+      </c>
+      <c r="C34" s="13">
+        <v>45</v>
+      </c>
+      <c r="D34" s="13">
+        <v>150</v>
+      </c>
+      <c r="E34" s="13">
+        <v>150</v>
+      </c>
+      <c r="F34" s="13">
+        <v>200</v>
+      </c>
+      <c r="G34" s="13">
+        <v>4</v>
+      </c>
+      <c r="H34" s="13">
+        <v>240</v>
+      </c>
+      <c r="I34" s="13">
+        <v>1145</v>
+      </c>
+      <c r="J34" s="13">
+        <v>295</v>
+      </c>
+      <c r="K34" s="13" t="s">
+        <v>25</v>
+      </c>
+      <c r="L34" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="M34" s="13" t="s">
+        <v>26</v>
+      </c>
+      <c r="N34" s="22" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="35" spans="1:14" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A35" s="26">
+        <v>46275</v>
+      </c>
+      <c r="B35" s="13">
+        <v>330</v>
+      </c>
+      <c r="C35" s="13">
+        <v>30</v>
+      </c>
+      <c r="D35" s="13">
+        <v>180</v>
+      </c>
+      <c r="E35" s="13">
+        <v>90</v>
+      </c>
+      <c r="F35" s="13">
+        <v>350</v>
+      </c>
+      <c r="G35" s="13">
+        <v>7</v>
+      </c>
+      <c r="H35" s="13">
+        <v>420</v>
+      </c>
+      <c r="I35" s="13">
+        <v>1400</v>
+      </c>
+      <c r="J35" s="13">
+        <v>40</v>
+      </c>
+      <c r="K35" s="13" t="s">
+        <v>68</v>
+      </c>
+      <c r="L35" s="13" t="s">
+        <v>30</v>
+      </c>
+      <c r="M35" s="13" t="s">
+        <v>29</v>
+      </c>
+      <c r="N35" s="22" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="36" spans="1:14" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A36" s="26">
+        <v>46276</v>
+      </c>
+      <c r="B36" s="13">
+        <v>360</v>
+      </c>
+      <c r="C36" s="13">
+        <v>30</v>
+      </c>
+      <c r="D36" s="13">
+        <v>180</v>
+      </c>
+      <c r="E36" s="13">
+        <v>120</v>
+      </c>
+      <c r="F36" s="13">
+        <v>350</v>
+      </c>
+      <c r="G36" s="13">
+        <v>7</v>
+      </c>
+      <c r="H36" s="13">
+        <v>300</v>
+      </c>
+      <c r="I36" s="13">
+        <v>1340</v>
+      </c>
+      <c r="J36" s="13">
+        <v>100</v>
+      </c>
+      <c r="K36" s="13" t="s">
+        <v>42</v>
+      </c>
+      <c r="L36" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="M36" s="13" t="s">
+        <v>29</v>
+      </c>
+      <c r="N36" s="22" t="s">
+        <v>70</v>
+      </c>
     </row>
     <row r="37" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A37" s="5"/>
@@ -2184,11 +2287,11 @@
       <c r="G37" s="6"/>
       <c r="H37" s="6"/>
       <c r="I37" s="4" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" ref="I37:I39" si="0">IF(SUM(B37:F37,H37)=0,"",SUM(B37:F37,H37))</f>
         <v/>
       </c>
       <c r="J37" s="4" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" ref="J37:J39" si="1">IF(I37="","",1440-I37)</f>
         <v/>
       </c>
       <c r="K37" s="7"/>
@@ -2250,11 +2353,11 @@
       <c r="G40" s="6"/>
       <c r="H40" s="6"/>
       <c r="I40" s="4" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" ref="I40:I103" si="2">IF(SUM(B40:F40,H40)=0,"",SUM(B40:F40,H40))</f>
         <v/>
       </c>
       <c r="J40" s="4" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" ref="J40:J103" si="3">IF(I40="","",1440-I40)</f>
         <v/>
       </c>
       <c r="K40" s="7"/>
@@ -2272,11 +2375,11 @@
       <c r="G41" s="6"/>
       <c r="H41" s="6"/>
       <c r="I41" s="4" t="str">
-        <f t="shared" ref="I41:I104" si="2">IF(SUM(B41:F41,H41)=0,"",SUM(B41:F41,H41))</f>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="J41" s="4" t="str">
-        <f t="shared" ref="J41:J104" si="3">IF(I41="","",1440-I41)</f>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="K41" s="7"/>
@@ -3658,11 +3761,11 @@
       <c r="G104" s="6"/>
       <c r="H104" s="6"/>
       <c r="I104" s="4" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" ref="I104:I167" si="4">IF(SUM(B104:F104,H104)=0,"",SUM(B104:F104,H104))</f>
         <v/>
       </c>
       <c r="J104" s="4" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" ref="J104:J167" si="5">IF(I104="","",1440-I104)</f>
         <v/>
       </c>
       <c r="K104" s="7"/>
@@ -3680,11 +3783,11 @@
       <c r="G105" s="6"/>
       <c r="H105" s="6"/>
       <c r="I105" s="4" t="str">
-        <f t="shared" ref="I105:I168" si="4">IF(SUM(B105:F105,H105)=0,"",SUM(B105:F105,H105))</f>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J105" s="4" t="str">
-        <f t="shared" ref="J105:J168" si="5">IF(I105="","",1440-I105)</f>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K105" s="7"/>
@@ -5066,11 +5169,11 @@
       <c r="G168" s="6"/>
       <c r="H168" s="6"/>
       <c r="I168" s="4" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" ref="I168:I231" si="6">IF(SUM(B168:F168,H168)=0,"",SUM(B168:F168,H168))</f>
         <v/>
       </c>
       <c r="J168" s="4" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" ref="J168:J231" si="7">IF(I168="","",1440-I168)</f>
         <v/>
       </c>
       <c r="K168" s="7"/>
@@ -5088,11 +5191,11 @@
       <c r="G169" s="6"/>
       <c r="H169" s="6"/>
       <c r="I169" s="4" t="str">
-        <f t="shared" ref="I169:I232" si="6">IF(SUM(B169:F169,H169)=0,"",SUM(B169:F169,H169))</f>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J169" s="4" t="str">
-        <f t="shared" ref="J169:J232" si="7">IF(I169="","",1440-I169)</f>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K169" s="7"/>
@@ -6474,11 +6577,11 @@
       <c r="G232" s="6"/>
       <c r="H232" s="6"/>
       <c r="I232" s="4" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" ref="I232:I295" si="8">IF(SUM(B232:F232,H232)=0,"",SUM(B232:F232,H232))</f>
         <v/>
       </c>
       <c r="J232" s="4" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" ref="J232:J295" si="9">IF(I232="","",1440-I232)</f>
         <v/>
       </c>
       <c r="K232" s="7"/>
@@ -6496,11 +6599,11 @@
       <c r="G233" s="6"/>
       <c r="H233" s="6"/>
       <c r="I233" s="4" t="str">
-        <f t="shared" ref="I233:I296" si="8">IF(SUM(B233:F233,H233)=0,"",SUM(B233:F233,H233))</f>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J233" s="4" t="str">
-        <f t="shared" ref="J233:J296" si="9">IF(I233="","",1440-I233)</f>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K233" s="7"/>
@@ -7882,11 +7985,11 @@
       <c r="G296" s="6"/>
       <c r="H296" s="6"/>
       <c r="I296" s="4" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" ref="I296:I359" si="10">IF(SUM(B296:F296,H296)=0,"",SUM(B296:F296,H296))</f>
         <v/>
       </c>
       <c r="J296" s="4" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" ref="J296:J359" si="11">IF(I296="","",1440-I296)</f>
         <v/>
       </c>
       <c r="K296" s="7"/>
@@ -7904,11 +8007,11 @@
       <c r="G297" s="6"/>
       <c r="H297" s="6"/>
       <c r="I297" s="4" t="str">
-        <f t="shared" ref="I297:I360" si="10">IF(SUM(B297:F297,H297)=0,"",SUM(B297:F297,H297))</f>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J297" s="4" t="str">
-        <f t="shared" ref="J297:J360" si="11">IF(I297="","",1440-I297)</f>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K297" s="7"/>
@@ -9290,11 +9393,11 @@
       <c r="G360" s="6"/>
       <c r="H360" s="6"/>
       <c r="I360" s="4" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" ref="I360:I372" si="12">IF(SUM(B360:F360,H360)=0,"",SUM(B360:F360,H360))</f>
         <v/>
       </c>
       <c r="J360" s="4" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" ref="J360:J372" si="13">IF(I360="","",1440-I360)</f>
         <v/>
       </c>
       <c r="K360" s="7"/>
@@ -9312,11 +9415,11 @@
       <c r="G361" s="6"/>
       <c r="H361" s="6"/>
       <c r="I361" s="4" t="str">
-        <f t="shared" ref="I361:I373" si="12">IF(SUM(B361:F361,H361)=0,"",SUM(B361:F361,H361))</f>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J361" s="4" t="str">
-        <f t="shared" ref="J361:J373" si="13">IF(I361="","",1440-I361)</f>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K361" s="7"/>
@@ -9523,14 +9626,6 @@
       <c r="N370" s="8"/>
     </row>
     <row r="371" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A371" s="5"/>
-      <c r="B371" s="6"/>
-      <c r="C371" s="6"/>
-      <c r="D371" s="6"/>
-      <c r="E371" s="6"/>
-      <c r="F371" s="6"/>
-      <c r="G371" s="6"/>
-      <c r="H371" s="6"/>
       <c r="I371" s="4" t="str">
         <f t="shared" si="12"/>
         <v/>
@@ -9539,10 +9634,6 @@
         <f t="shared" si="13"/>
         <v/>
       </c>
-      <c r="K371" s="7"/>
-      <c r="L371" s="7"/>
-      <c r="M371" s="7"/>
-      <c r="N371" s="8"/>
     </row>
     <row r="372" spans="1:14" x14ac:dyDescent="0.3">
       <c r="I372" s="4" t="str">
@@ -9550,16 +9641,6 @@
         <v/>
       </c>
       <c r="J372" s="4" t="str">
-        <f t="shared" si="13"/>
-        <v/>
-      </c>
-    </row>
-    <row r="373" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="I373" s="4" t="str">
-        <f t="shared" si="12"/>
-        <v/>
-      </c>
-      <c r="J373" s="4" t="str">
         <f t="shared" si="13"/>
         <v/>
       </c>
